--- a/research/traditional_assets/database/data/turkey/turkey_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1310086682408267</v>
+        <v>0.1307148965702246</v>
       </c>
       <c r="C2">
-        <v>1562.417972012173</v>
+        <v>1551.392265582793</v>
       </c>
       <c r="D2">
-        <v>1290.117972012173</v>
+        <v>1294.581265582793</v>
       </c>
       <c r="E2">
-        <v>-144.3</v>
+        <v>-128.811</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.489</v>
       </c>
       <c r="G2">
         <v>272.3</v>
@@ -1451,28 +1451,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7790966999999999</v>
       </c>
       <c r="N2">
-        <v>101.6666666666667</v>
+        <v>100.8875699666667</v>
       </c>
       <c r="O2">
-        <v>25.41666666666667</v>
+        <v>25.22189249166667</v>
       </c>
       <c r="P2">
-        <v>76.25</v>
+        <v>75.66567747500001</v>
       </c>
       <c r="Q2">
-        <v>85.25</v>
+        <v>84.66567747500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1310086682408267</v>
+        <v>0.1316541884547724</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8302756192024354</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>130.4930012752803</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1307148965702246</v>
+        <v>0.1304211248996226</v>
       </c>
       <c r="C3">
-        <v>1551.392265582793</v>
+        <v>1540.397548796016</v>
       </c>
       <c r="D3">
-        <v>1294.581265582793</v>
+        <v>1299.075548796016</v>
       </c>
       <c r="E3">
-        <v>-128.811</v>
+        <v>-113.322</v>
       </c>
       <c r="F3">
-        <v>15.489</v>
+        <v>30.978</v>
       </c>
       <c r="G3">
         <v>272.3</v>
@@ -1533,28 +1533,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M3">
-        <v>0.7790966999999999</v>
+        <v>1.5581934</v>
       </c>
       <c r="N3">
-        <v>100.8875699666667</v>
+        <v>100.1084732666667</v>
       </c>
       <c r="O3">
-        <v>25.22189249166667</v>
+        <v>25.02711831666667</v>
       </c>
       <c r="P3">
-        <v>75.66567747500001</v>
+        <v>75.08135495000001</v>
       </c>
       <c r="Q3">
-        <v>84.66567747500001</v>
+        <v>84.08135495000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1316541884547724</v>
+        <v>0.1323128825506353</v>
       </c>
       <c r="T3">
-        <v>0.8302756192024354</v>
+        <v>0.8366456945377311</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>130.4930012752803</v>
+        <v>65.24650063764017</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1304211248996226</v>
+        <v>0.1301273532290205</v>
       </c>
       <c r="C4">
-        <v>1540.397548796016</v>
+        <v>1529.434145528213</v>
       </c>
       <c r="D4">
-        <v>1299.075548796016</v>
+        <v>1303.601145528213</v>
       </c>
       <c r="E4">
-        <v>-113.322</v>
+        <v>-97.83300000000003</v>
       </c>
       <c r="F4">
-        <v>30.978</v>
+        <v>46.46699999999999</v>
       </c>
       <c r="G4">
         <v>272.3</v>
@@ -1615,28 +1615,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M4">
-        <v>1.5581934</v>
+        <v>2.337290099999999</v>
       </c>
       <c r="N4">
-        <v>100.1084732666667</v>
+        <v>99.32937656666667</v>
       </c>
       <c r="O4">
-        <v>25.02711831666667</v>
+        <v>24.83234414166667</v>
       </c>
       <c r="P4">
-        <v>75.08135495000001</v>
+        <v>74.497032425</v>
       </c>
       <c r="Q4">
-        <v>84.08135495000001</v>
+        <v>83.497032425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1323128825506353</v>
+        <v>0.1329851579680624</v>
       </c>
       <c r="T4">
-        <v>0.8366456945377311</v>
+        <v>0.8431471116325172</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.24650063764017</v>
+        <v>43.49766709176011</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1301273532290205</v>
+        <v>0.1298335815584184</v>
       </c>
       <c r="C5">
-        <v>1529.434145528213</v>
+        <v>1518.502384184695</v>
       </c>
       <c r="D5">
-        <v>1303.601145528213</v>
+        <v>1308.158384184695</v>
       </c>
       <c r="E5">
-        <v>-97.83300000000003</v>
+        <v>-82.34400000000002</v>
       </c>
       <c r="F5">
-        <v>46.46699999999999</v>
+        <v>61.956</v>
       </c>
       <c r="G5">
         <v>272.3</v>
@@ -1697,28 +1697,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M5">
-        <v>2.337290099999999</v>
+        <v>3.116386799999999</v>
       </c>
       <c r="N5">
-        <v>99.32937656666667</v>
+        <v>98.55027986666667</v>
       </c>
       <c r="O5">
-        <v>24.83234414166667</v>
+        <v>24.63756996666667</v>
       </c>
       <c r="P5">
-        <v>74.497032425</v>
+        <v>73.91270990000001</v>
       </c>
       <c r="Q5">
-        <v>83.497032425</v>
+        <v>82.91270990000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1329851579680624</v>
+        <v>0.1336714391233525</v>
       </c>
       <c r="T5">
-        <v>0.8431471116325172</v>
+        <v>0.8497839749167783</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.49766709176011</v>
+        <v>32.62325031882008</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1298335815584184</v>
+        <v>0.1295398098878164</v>
       </c>
       <c r="C6">
-        <v>1518.502384184695</v>
+        <v>1507.602597779147</v>
       </c>
       <c r="D6">
-        <v>1308.158384184695</v>
+        <v>1312.747597779147</v>
       </c>
       <c r="E6">
-        <v>-82.34400000000002</v>
+        <v>-66.85500000000002</v>
       </c>
       <c r="F6">
-        <v>61.956</v>
+        <v>77.44499999999999</v>
       </c>
       <c r="G6">
         <v>272.3</v>
@@ -1779,28 +1779,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M6">
-        <v>3.116386799999999</v>
+        <v>3.8954835</v>
       </c>
       <c r="N6">
-        <v>98.55027986666667</v>
+        <v>97.77118316666667</v>
       </c>
       <c r="O6">
-        <v>24.63756996666667</v>
+        <v>24.44279579166667</v>
       </c>
       <c r="P6">
-        <v>73.91270990000001</v>
+        <v>73.32838737500001</v>
       </c>
       <c r="Q6">
-        <v>82.91270990000001</v>
+        <v>82.32838737500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1336714391233525</v>
+        <v>0.1343721683029646</v>
       </c>
       <c r="T6">
-        <v>0.8497839749167783</v>
+        <v>0.8565605616386027</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.62325031882008</v>
+        <v>26.09860025505606</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1295398098878164</v>
+        <v>0.1292460382172143</v>
       </c>
       <c r="C7">
-        <v>1507.602597779147</v>
+        <v>1496.735124014755</v>
       </c>
       <c r="D7">
-        <v>1312.747597779147</v>
+        <v>1317.369124014755</v>
       </c>
       <c r="E7">
-        <v>-66.85500000000002</v>
+        <v>-51.36600000000001</v>
       </c>
       <c r="F7">
-        <v>77.44499999999999</v>
+        <v>92.934</v>
       </c>
       <c r="G7">
         <v>272.3</v>
@@ -1861,28 +1861,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M7">
-        <v>3.8954835</v>
+        <v>4.674580199999999</v>
       </c>
       <c r="N7">
-        <v>97.77118316666667</v>
+        <v>96.99208646666668</v>
       </c>
       <c r="O7">
-        <v>24.44279579166667</v>
+        <v>24.24802161666667</v>
       </c>
       <c r="P7">
-        <v>73.32838737500001</v>
+        <v>72.74406485</v>
       </c>
       <c r="Q7">
-        <v>82.32838737500001</v>
+        <v>81.74406485</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1343721683029646</v>
+        <v>0.1350878066140578</v>
       </c>
       <c r="T7">
-        <v>0.8565605616386027</v>
+        <v>0.8634813310566362</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.09860025505606</v>
+        <v>21.74883354588005</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1292460382172143</v>
+        <v>0.1289522665466122</v>
       </c>
       <c r="C8">
-        <v>1496.735124014755</v>
+        <v>1485.900305367039</v>
       </c>
       <c r="D8">
-        <v>1317.369124014755</v>
+        <v>1322.023305367039</v>
       </c>
       <c r="E8">
-        <v>-51.36600000000003</v>
+        <v>-35.87700000000004</v>
       </c>
       <c r="F8">
-        <v>92.93399999999998</v>
+        <v>108.423</v>
       </c>
       <c r="G8">
         <v>272.3</v>
@@ -1943,28 +1943,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M8">
-        <v>4.674580199999999</v>
+        <v>5.453676899999999</v>
       </c>
       <c r="N8">
-        <v>96.99208646666668</v>
+        <v>96.21298976666667</v>
       </c>
       <c r="O8">
-        <v>24.24802161666667</v>
+        <v>24.05324744166667</v>
       </c>
       <c r="P8">
-        <v>72.74406485</v>
+        <v>72.159742325</v>
       </c>
       <c r="Q8">
-        <v>81.74406485</v>
+        <v>81.159742325</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1350878066140578</v>
+        <v>0.1358188349963572</v>
       </c>
       <c r="T8">
-        <v>0.8634813310566362</v>
+        <v>0.8705509342255949</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.74883354588006</v>
+        <v>18.64185732504005</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1289522665466122</v>
+        <v>0.1286584948760102</v>
       </c>
       <c r="C9">
-        <v>1485.900305367039</v>
+        <v>1475.098489168455</v>
       </c>
       <c r="D9">
-        <v>1322.023305367039</v>
+        <v>1326.710489168456</v>
       </c>
       <c r="E9">
-        <v>-35.87700000000001</v>
+        <v>-20.38800000000002</v>
       </c>
       <c r="F9">
-        <v>108.423</v>
+        <v>123.912</v>
       </c>
       <c r="G9">
         <v>272.3</v>
@@ -2025,28 +2025,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M9">
-        <v>5.4536769</v>
+        <v>6.232773599999999</v>
       </c>
       <c r="N9">
-        <v>96.21298976666667</v>
+        <v>95.43389306666667</v>
       </c>
       <c r="O9">
-        <v>24.05324744166667</v>
+        <v>23.85847326666667</v>
       </c>
       <c r="P9">
-        <v>72.159742325</v>
+        <v>71.57541980000001</v>
       </c>
       <c r="Q9">
-        <v>81.159742325</v>
+        <v>80.57541980000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1358188349963572</v>
+        <v>0.1365657553000111</v>
       </c>
       <c r="T9">
-        <v>0.8705509342255949</v>
+        <v>0.8777742244199661</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.64185732504004</v>
+        <v>16.31162515941004</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1286584948760102</v>
+        <v>0.1283647232054081</v>
       </c>
       <c r="C10">
-        <v>1475.098489168455</v>
+        <v>1464.330027694802</v>
       </c>
       <c r="D10">
-        <v>1326.710489168456</v>
+        <v>1331.431027694802</v>
       </c>
       <c r="E10">
-        <v>-20.38800000000002</v>
+        <v>-4.899000000000029</v>
       </c>
       <c r="F10">
-        <v>123.912</v>
+        <v>139.401</v>
       </c>
       <c r="G10">
         <v>272.3</v>
@@ -2107,28 +2107,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M10">
-        <v>6.232773599999999</v>
+        <v>7.011870299999999</v>
       </c>
       <c r="N10">
-        <v>95.43389306666667</v>
+        <v>94.65479636666667</v>
       </c>
       <c r="O10">
-        <v>23.85847326666667</v>
+        <v>23.66369909166667</v>
       </c>
       <c r="P10">
-        <v>71.57541980000001</v>
+        <v>70.991097275</v>
       </c>
       <c r="Q10">
-        <v>80.57541980000001</v>
+        <v>79.991097275</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1365657553000111</v>
+        <v>0.1373290914345144</v>
       </c>
       <c r="T10">
-        <v>0.8777742244199661</v>
+        <v>0.8851562682449825</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.31162515941004</v>
+        <v>14.49922236392004</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1283647232054081</v>
+        <v>0.128070951534806</v>
       </c>
       <c r="C11">
-        <v>1464.330027694802</v>
+        <v>1453.595278253481</v>
       </c>
       <c r="D11">
-        <v>1331.431027694802</v>
+        <v>1336.18527825348</v>
       </c>
       <c r="E11">
-        <v>-4.899000000000029</v>
+        <v>10.58999999999997</v>
       </c>
       <c r="F11">
-        <v>139.401</v>
+        <v>154.89</v>
       </c>
       <c r="G11">
         <v>272.3</v>
@@ -2189,28 +2189,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M11">
-        <v>7.011870299999999</v>
+        <v>7.790966999999999</v>
       </c>
       <c r="N11">
-        <v>94.65479636666667</v>
+        <v>93.87569966666668</v>
       </c>
       <c r="O11">
-        <v>23.66369909166667</v>
+        <v>23.46892491666667</v>
       </c>
       <c r="P11">
-        <v>70.991097275</v>
+        <v>70.40677475000001</v>
       </c>
       <c r="Q11">
-        <v>79.991097275</v>
+        <v>79.40677475000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1373290914345144</v>
+        <v>0.1381093905942289</v>
       </c>
       <c r="T11">
-        <v>0.8851562682449825</v>
+        <v>0.8927023574883327</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.49922236392004</v>
+        <v>13.04930012752803</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.128070951534806</v>
+        <v>0.127900929864204</v>
       </c>
       <c r="C12">
-        <v>1453.595278253481</v>
+        <v>1440.873365710569</v>
       </c>
       <c r="D12">
-        <v>1336.18527825348</v>
+        <v>1338.952365710569</v>
       </c>
       <c r="E12">
-        <v>10.58999999999997</v>
+        <v>26.07899999999998</v>
       </c>
       <c r="F12">
-        <v>154.89</v>
+        <v>170.379</v>
       </c>
       <c r="G12">
         <v>272.3</v>
@@ -2271,45 +2271,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M12">
-        <v>7.790966999999999</v>
+        <v>8.825632199999999</v>
       </c>
       <c r="N12">
-        <v>93.87569966666668</v>
+        <v>92.84103446666667</v>
       </c>
       <c r="O12">
-        <v>23.46892491666667</v>
+        <v>23.21025861666667</v>
       </c>
       <c r="P12">
-        <v>70.40677475000001</v>
+        <v>69.63077585000001</v>
       </c>
       <c r="Q12">
-        <v>79.40677475000001</v>
+        <v>78.63077585000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1381093905942289</v>
+        <v>0.1389072245665213</v>
       </c>
       <c r="T12">
-        <v>0.8927023574883327</v>
+        <v>0.9004180217708595</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.04930012752803</v>
+        <v>11.51947694655423</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.127900929864204</v>
+        <v>0.1276184081936019</v>
       </c>
       <c r="C13">
-        <v>1440.873365710569</v>
+        <v>1430.007812531021</v>
       </c>
       <c r="D13">
-        <v>1338.952365710569</v>
+        <v>1343.575812531021</v>
       </c>
       <c r="E13">
-        <v>26.07899999999998</v>
+        <v>41.56799999999996</v>
       </c>
       <c r="F13">
-        <v>170.379</v>
+        <v>185.868</v>
       </c>
       <c r="G13">
         <v>272.3</v>
@@ -2353,28 +2353,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M13">
-        <v>8.825632199999999</v>
+        <v>9.627962399999998</v>
       </c>
       <c r="N13">
-        <v>92.84103446666667</v>
+        <v>92.03870426666667</v>
       </c>
       <c r="O13">
-        <v>23.21025861666667</v>
+        <v>23.00967606666667</v>
       </c>
       <c r="P13">
-        <v>69.63077585000001</v>
+        <v>69.0290282</v>
       </c>
       <c r="Q13">
-        <v>78.63077585000001</v>
+        <v>78.0290282</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1389072245665213</v>
+        <v>0.1397231911290931</v>
       </c>
       <c r="T13">
-        <v>0.9004180217708595</v>
+        <v>0.9083090420598071</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.51947694655423</v>
+        <v>10.55952053434138</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1276184081936019</v>
+        <v>0.1275016365229998</v>
       </c>
       <c r="C14">
-        <v>1430.007812531021</v>
+        <v>1416.43911179168</v>
       </c>
       <c r="D14">
-        <v>1343.575812531021</v>
+        <v>1345.49611179168</v>
       </c>
       <c r="E14">
-        <v>41.56799999999996</v>
+        <v>57.05699999999999</v>
       </c>
       <c r="F14">
-        <v>185.868</v>
+        <v>201.357</v>
       </c>
       <c r="G14">
         <v>272.3</v>
@@ -2435,45 +2435,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M14">
-        <v>9.627962399999998</v>
+        <v>10.7725995</v>
       </c>
       <c r="N14">
-        <v>92.03870426666667</v>
+        <v>90.89406716666667</v>
       </c>
       <c r="O14">
-        <v>23.00967606666667</v>
+        <v>22.72351679166667</v>
       </c>
       <c r="P14">
-        <v>69.0290282</v>
+        <v>68.170550375</v>
       </c>
       <c r="Q14">
-        <v>78.0290282</v>
+        <v>77.170550375</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1397231911290931</v>
+        <v>0.140557915543678</v>
       </c>
       <c r="T14">
-        <v>0.9083090420598071</v>
+        <v>0.916381465114018</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.55952053434138</v>
+        <v>9.437524031842702</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1275016365229998</v>
+        <v>0.1272318648523978</v>
       </c>
       <c r="C15">
-        <v>1416.43911179168</v>
+        <v>1405.407540520895</v>
       </c>
       <c r="D15">
-        <v>1345.49611179168</v>
+        <v>1349.953540520895</v>
       </c>
       <c r="E15">
-        <v>57.05699999999999</v>
+        <v>72.54599999999999</v>
       </c>
       <c r="F15">
-        <v>201.357</v>
+        <v>216.846</v>
       </c>
       <c r="G15">
         <v>272.3</v>
@@ -2517,28 +2517,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M15">
-        <v>10.7725995</v>
+        <v>11.601261</v>
       </c>
       <c r="N15">
-        <v>90.89406716666667</v>
+        <v>90.06540566666668</v>
       </c>
       <c r="O15">
-        <v>22.72351679166667</v>
+        <v>22.51635141666667</v>
       </c>
       <c r="P15">
-        <v>68.170550375</v>
+        <v>67.54905425000001</v>
       </c>
       <c r="Q15">
-        <v>77.170550375</v>
+        <v>76.54905425000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.140557915543678</v>
+        <v>0.1414120521539509</v>
       </c>
       <c r="T15">
-        <v>0.916381465114018</v>
+        <v>0.9246416189369314</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.437524031842702</v>
+        <v>8.763415172425367</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1272318648523978</v>
+        <v>0.1269620931817957</v>
       </c>
       <c r="C16">
-        <v>1405.407540520895</v>
+        <v>1394.405601014096</v>
       </c>
       <c r="D16">
-        <v>1349.953540520895</v>
+        <v>1354.440601014096</v>
       </c>
       <c r="E16">
-        <v>72.54599999999999</v>
+        <v>88.035</v>
       </c>
       <c r="F16">
-        <v>216.846</v>
+        <v>232.335</v>
       </c>
       <c r="G16">
         <v>272.3</v>
@@ -2599,28 +2599,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M16">
-        <v>11.601261</v>
+        <v>12.4299225</v>
       </c>
       <c r="N16">
-        <v>90.06540566666668</v>
+        <v>89.23674416666667</v>
       </c>
       <c r="O16">
-        <v>22.51635141666667</v>
+        <v>22.30918604166667</v>
       </c>
       <c r="P16">
-        <v>67.54905425000001</v>
+        <v>66.927558125</v>
       </c>
       <c r="Q16">
-        <v>76.54905425000001</v>
+        <v>75.927558125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1414120521539509</v>
+        <v>0.1422862860962302</v>
       </c>
       <c r="T16">
-        <v>0.9246416189369314</v>
+        <v>0.933096129320384</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.763415172425367</v>
+        <v>8.179187494263674</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1269620931817957</v>
+        <v>0.1266923215111936</v>
       </c>
       <c r="C17">
-        <v>1394.405601014096</v>
+        <v>1383.433589732442</v>
       </c>
       <c r="D17">
-        <v>1354.440601014096</v>
+        <v>1358.957589732442</v>
       </c>
       <c r="E17">
-        <v>88.03499999999997</v>
+        <v>103.524</v>
       </c>
       <c r="F17">
-        <v>232.335</v>
+        <v>247.824</v>
       </c>
       <c r="G17">
         <v>272.3</v>
@@ -2681,28 +2681,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M17">
-        <v>12.4299225</v>
+        <v>13.258584</v>
       </c>
       <c r="N17">
-        <v>89.23674416666667</v>
+        <v>88.40808266666667</v>
       </c>
       <c r="O17">
-        <v>22.30918604166667</v>
+        <v>22.10202066666667</v>
       </c>
       <c r="P17">
-        <v>66.927558125</v>
+        <v>66.306062</v>
       </c>
       <c r="Q17">
-        <v>75.927558125</v>
+        <v>75.306062</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1422862860962302</v>
+        <v>0.1431813351323734</v>
       </c>
       <c r="T17">
-        <v>0.933096129320384</v>
+        <v>0.9417519375701092</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.179187494263676</v>
+        <v>7.667988275872196</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1266923215111936</v>
+        <v>0.1265245498405916</v>
       </c>
       <c r="C18">
-        <v>1383.433589732442</v>
+        <v>1370.768942244248</v>
       </c>
       <c r="D18">
-        <v>1358.957589732442</v>
+        <v>1361.781942244248</v>
       </c>
       <c r="E18">
-        <v>103.524</v>
+        <v>119.013</v>
       </c>
       <c r="F18">
-        <v>247.824</v>
+        <v>263.313</v>
       </c>
       <c r="G18">
         <v>272.3</v>
@@ -2763,45 +2763,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M18">
-        <v>13.258584</v>
+        <v>14.2978959</v>
       </c>
       <c r="N18">
-        <v>88.40808266666667</v>
+        <v>87.36877076666667</v>
       </c>
       <c r="O18">
-        <v>22.10202066666667</v>
+        <v>21.84219269166667</v>
       </c>
       <c r="P18">
-        <v>66.306062</v>
+        <v>65.526578075</v>
       </c>
       <c r="Q18">
-        <v>75.306062</v>
+        <v>74.526578075</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1431813351323734</v>
+        <v>0.1440979516151706</v>
       </c>
       <c r="T18">
-        <v>0.9417519375701092</v>
+        <v>0.9506163195125992</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.667988275872196</v>
+        <v>7.110603362741413</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1265245498405916</v>
+        <v>0.1262607781699895</v>
       </c>
       <c r="C19">
-        <v>1370.768942244248</v>
+        <v>1359.744222929461</v>
       </c>
       <c r="D19">
-        <v>1361.781942244248</v>
+        <v>1366.246222929461</v>
       </c>
       <c r="E19">
-        <v>119.013</v>
+        <v>134.502</v>
       </c>
       <c r="F19">
-        <v>263.313</v>
+        <v>278.802</v>
       </c>
       <c r="G19">
         <v>272.3</v>
@@ -2845,28 +2845,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M19">
-        <v>14.2978959</v>
+        <v>15.1389486</v>
       </c>
       <c r="N19">
-        <v>87.36877076666667</v>
+        <v>86.52771806666667</v>
       </c>
       <c r="O19">
-        <v>21.84219269166667</v>
+        <v>21.63192951666667</v>
       </c>
       <c r="P19">
-        <v>65.526578075</v>
+        <v>64.89578854999999</v>
       </c>
       <c r="Q19">
-        <v>74.526578075</v>
+        <v>73.89578854999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1440979516151706</v>
+        <v>0.1450369245975482</v>
       </c>
       <c r="T19">
-        <v>0.9506163195125992</v>
+        <v>0.9596969058927104</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.110603362741413</v>
+        <v>6.715569842589113</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1262607781699895</v>
+        <v>0.1259970064993874</v>
       </c>
       <c r="C20">
-        <v>1359.744222929461</v>
+        <v>1348.748870066759</v>
       </c>
       <c r="D20">
-        <v>1366.246222929461</v>
+        <v>1370.739870066759</v>
       </c>
       <c r="E20">
-        <v>134.502</v>
+        <v>149.991</v>
       </c>
       <c r="F20">
-        <v>278.802</v>
+        <v>294.291</v>
       </c>
       <c r="G20">
         <v>272.3</v>
@@ -2927,28 +2927,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M20">
-        <v>15.1389486</v>
+        <v>15.9800013</v>
       </c>
       <c r="N20">
-        <v>86.52771806666667</v>
+        <v>85.68666536666667</v>
       </c>
       <c r="O20">
-        <v>21.63192951666667</v>
+        <v>21.42166634166667</v>
       </c>
       <c r="P20">
-        <v>64.89578854999999</v>
+        <v>64.26499902500001</v>
       </c>
       <c r="Q20">
-        <v>73.89578854999999</v>
+        <v>73.26499902500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1450369245975482</v>
+        <v>0.1459990820980092</v>
       </c>
       <c r="T20">
-        <v>0.9596969058927104</v>
+        <v>0.9690017042822074</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.715569842589113</v>
+        <v>6.362118798242318</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1259970064993874</v>
+        <v>0.1258832348287854</v>
       </c>
       <c r="C21">
-        <v>1348.748870066759</v>
+        <v>1335.207236020592</v>
       </c>
       <c r="D21">
-        <v>1370.739870066759</v>
+        <v>1372.687236020592</v>
       </c>
       <c r="E21">
-        <v>149.991</v>
+        <v>165.48</v>
       </c>
       <c r="F21">
-        <v>294.291</v>
+        <v>309.78</v>
       </c>
       <c r="G21">
         <v>272.3</v>
@@ -3009,45 +3009,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M21">
-        <v>15.9800013</v>
+        <v>17.130834</v>
       </c>
       <c r="N21">
-        <v>85.68666536666667</v>
+        <v>84.53583266666666</v>
       </c>
       <c r="O21">
-        <v>21.42166634166667</v>
+        <v>21.13395816666667</v>
       </c>
       <c r="P21">
-        <v>64.26499902500001</v>
+        <v>63.4018745</v>
       </c>
       <c r="Q21">
-        <v>73.26499902500001</v>
+        <v>72.40187449999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1459990820980092</v>
+        <v>0.1469852935359817</v>
       </c>
       <c r="T21">
-        <v>0.9690017042822074</v>
+        <v>0.9785391226314417</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.362118798242318</v>
+        <v>5.934717869933634</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1258832348287854</v>
+        <v>0.1256269631581833</v>
       </c>
       <c r="C22">
-        <v>1335.207236020592</v>
+        <v>1324.125028378358</v>
       </c>
       <c r="D22">
-        <v>1372.687236020592</v>
+        <v>1377.094028378358</v>
       </c>
       <c r="E22">
-        <v>165.48</v>
+        <v>180.969</v>
       </c>
       <c r="F22">
-        <v>309.78</v>
+        <v>325.269</v>
       </c>
       <c r="G22">
         <v>272.3</v>
@@ -3091,28 +3091,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M22">
-        <v>17.130834</v>
+        <v>17.9873757</v>
       </c>
       <c r="N22">
-        <v>84.53583266666666</v>
+        <v>83.67929096666667</v>
       </c>
       <c r="O22">
-        <v>21.13395816666667</v>
+        <v>20.91982274166667</v>
       </c>
       <c r="P22">
-        <v>63.4018745</v>
+        <v>62.75946822500001</v>
       </c>
       <c r="Q22">
-        <v>72.40187449999999</v>
+        <v>71.75946822500001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1469852935359817</v>
+        <v>0.1479964723521308</v>
       </c>
       <c r="T22">
-        <v>0.9785391226314417</v>
+        <v>0.9883179946097705</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.934717869933634</v>
+        <v>5.652112257079651</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1256269631581833</v>
+        <v>0.1253706914875812</v>
       </c>
       <c r="C23">
-        <v>1324.125028378358</v>
+        <v>1313.07120646505</v>
       </c>
       <c r="D23">
-        <v>1377.094028378358</v>
+        <v>1381.52920646505</v>
       </c>
       <c r="E23">
-        <v>180.9689999999999</v>
+        <v>196.458</v>
       </c>
       <c r="F23">
-        <v>325.2689999999999</v>
+        <v>340.758</v>
       </c>
       <c r="G23">
         <v>272.3</v>
@@ -3173,28 +3173,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M23">
-        <v>17.9873757</v>
+        <v>18.8439174</v>
       </c>
       <c r="N23">
-        <v>83.67929096666667</v>
+        <v>82.82274926666668</v>
       </c>
       <c r="O23">
-        <v>20.91982274166667</v>
+        <v>20.70568731666667</v>
       </c>
       <c r="P23">
-        <v>62.75946822500001</v>
+        <v>62.11706195000001</v>
       </c>
       <c r="Q23">
-        <v>71.75946822500001</v>
+        <v>71.11706195000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1479964723521308</v>
+        <v>0.1490335788302323</v>
       </c>
       <c r="T23">
-        <v>0.9883179946097705</v>
+        <v>0.9983476068952359</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.652112257079652</v>
+        <v>5.395198063576031</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1253706914875812</v>
+        <v>0.1251144198169792</v>
       </c>
       <c r="C24">
-        <v>1313.07120646505</v>
+        <v>1302.046045430819</v>
       </c>
       <c r="D24">
-        <v>1381.52920646505</v>
+        <v>1385.993045430818</v>
       </c>
       <c r="E24">
-        <v>196.458</v>
+        <v>211.9469999999999</v>
       </c>
       <c r="F24">
-        <v>340.758</v>
+        <v>356.247</v>
       </c>
       <c r="G24">
         <v>272.3</v>
@@ -3255,28 +3255,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M24">
-        <v>18.8439174</v>
+        <v>19.7004591</v>
       </c>
       <c r="N24">
-        <v>82.82274926666668</v>
+        <v>81.96620756666667</v>
       </c>
       <c r="O24">
-        <v>20.70568731666667</v>
+        <v>20.49155189166667</v>
       </c>
       <c r="P24">
-        <v>62.11706195000001</v>
+        <v>61.474655675</v>
       </c>
       <c r="Q24">
-        <v>71.11706195000001</v>
+        <v>70.47465567500001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1490335788302323</v>
+        <v>0.150097623138934</v>
       </c>
       <c r="T24">
-        <v>0.9983476068952359</v>
+        <v>1.008637728590714</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.395198063576031</v>
+        <v>5.160624234724899</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1251144198169792</v>
+        <v>0.1248581481463771</v>
       </c>
       <c r="C25">
-        <v>1302.046045430819</v>
+        <v>1291.049823993475</v>
       </c>
       <c r="D25">
-        <v>1385.993045430818</v>
+        <v>1390.485823993475</v>
       </c>
       <c r="E25">
-        <v>211.9469999999999</v>
+        <v>227.436</v>
       </c>
       <c r="F25">
-        <v>356.247</v>
+        <v>371.736</v>
       </c>
       <c r="G25">
         <v>272.3</v>
@@ -3337,28 +3337,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M25">
-        <v>19.7004591</v>
+        <v>20.5570008</v>
       </c>
       <c r="N25">
-        <v>81.96620756666667</v>
+        <v>81.10966586666667</v>
       </c>
       <c r="O25">
-        <v>20.49155189166667</v>
+        <v>20.27741646666667</v>
       </c>
       <c r="P25">
-        <v>61.474655675</v>
+        <v>60.83224940000001</v>
       </c>
       <c r="Q25">
-        <v>70.47465567500001</v>
+        <v>69.83224940000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.150097623138934</v>
+        <v>0.1511896686136541</v>
       </c>
       <c r="T25">
-        <v>1.008637728590714</v>
+        <v>1.019198642962388</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.160624234724899</v>
+        <v>4.945598224944694</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1248581481463771</v>
+        <v>0.124601876475775</v>
       </c>
       <c r="C26">
-        <v>1291.049823993475</v>
+        <v>1280.082824496507</v>
       </c>
       <c r="D26">
-        <v>1390.485823993475</v>
+        <v>1395.007824496507</v>
       </c>
       <c r="E26">
-        <v>227.4359999999999</v>
+        <v>242.925</v>
       </c>
       <c r="F26">
-        <v>371.7359999999999</v>
+        <v>387.225</v>
       </c>
       <c r="G26">
         <v>272.3</v>
@@ -3419,28 +3419,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M26">
-        <v>20.5570008</v>
+        <v>21.4135425</v>
       </c>
       <c r="N26">
-        <v>81.10966586666667</v>
+        <v>80.25312416666668</v>
       </c>
       <c r="O26">
-        <v>20.27741646666667</v>
+        <v>20.06328104166667</v>
       </c>
       <c r="P26">
-        <v>60.83224940000001</v>
+        <v>60.18984312500001</v>
       </c>
       <c r="Q26">
-        <v>69.83224940000001</v>
+        <v>69.18984312500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1511896686136541</v>
+        <v>0.1523108353010334</v>
       </c>
       <c r="T26">
-        <v>1.019198642962388</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.945598224944695</v>
+        <v>4.747774295946908</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.124601876475775</v>
+        <v>0.124345604805173</v>
       </c>
       <c r="C27">
-        <v>1280.082824496507</v>
+        <v>1269.145332968221</v>
       </c>
       <c r="D27">
-        <v>1395.007824496507</v>
+        <v>1399.559332968221</v>
       </c>
       <c r="E27">
-        <v>242.925</v>
+        <v>258.414</v>
       </c>
       <c r="F27">
-        <v>387.225</v>
+        <v>402.714</v>
       </c>
       <c r="G27">
         <v>272.3</v>
@@ -3501,28 +3501,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M27">
-        <v>21.4135425</v>
+        <v>22.2700842</v>
       </c>
       <c r="N27">
-        <v>80.25312416666668</v>
+        <v>79.39658246666667</v>
       </c>
       <c r="O27">
-        <v>20.06328104166667</v>
+        <v>19.84914561666667</v>
       </c>
       <c r="P27">
-        <v>60.18984312500001</v>
+        <v>59.54743685</v>
       </c>
       <c r="Q27">
-        <v>69.18984312500001</v>
+        <v>68.54743685</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1523108353010334</v>
+        <v>0.1534623037907743</v>
       </c>
       <c r="T27">
-        <v>1.030041181717307</v>
+        <v>1.041176762060197</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.747774295946908</v>
+        <v>4.565167592256642</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.124345604805173</v>
+        <v>0.1245955831345709</v>
       </c>
       <c r="C28">
-        <v>1269.145332968221</v>
+        <v>1249.216242673424</v>
       </c>
       <c r="D28">
-        <v>1399.559332968221</v>
+        <v>1395.119242673424</v>
       </c>
       <c r="E28">
-        <v>258.414</v>
+        <v>273.903</v>
       </c>
       <c r="F28">
-        <v>402.714</v>
+        <v>418.203</v>
       </c>
       <c r="G28">
         <v>272.3</v>
@@ -3583,45 +3583,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M28">
-        <v>22.2700842</v>
+        <v>24.1721334</v>
       </c>
       <c r="N28">
-        <v>79.39658246666667</v>
+        <v>77.49453326666668</v>
       </c>
       <c r="O28">
-        <v>19.84914561666667</v>
+        <v>19.37363331666667</v>
       </c>
       <c r="P28">
-        <v>59.54743685</v>
+        <v>58.12089995000001</v>
       </c>
       <c r="Q28">
-        <v>68.54743685</v>
+        <v>67.12089995000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1534623037907743</v>
+        <v>0.1546453193624259</v>
       </c>
       <c r="T28">
-        <v>1.041176762060197</v>
+        <v>1.052617426796043</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.565167592256642</v>
+        <v>4.205945126327437</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1245955831345709</v>
+        <v>0.1243580614639688</v>
       </c>
       <c r="C29">
-        <v>1249.216242673424</v>
+        <v>1237.945410064951</v>
       </c>
       <c r="D29">
-        <v>1395.119242673424</v>
+        <v>1399.337410064951</v>
       </c>
       <c r="E29">
-        <v>273.903</v>
+        <v>289.392</v>
       </c>
       <c r="F29">
-        <v>418.203</v>
+        <v>433.692</v>
       </c>
       <c r="G29">
         <v>272.3</v>
@@ -3665,28 +3665,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M29">
-        <v>24.1721334</v>
+        <v>25.0673976</v>
       </c>
       <c r="N29">
-        <v>77.49453326666668</v>
+        <v>76.59926906666666</v>
       </c>
       <c r="O29">
-        <v>19.37363331666667</v>
+        <v>19.14981726666667</v>
       </c>
       <c r="P29">
-        <v>58.12089995000001</v>
+        <v>57.4494518</v>
       </c>
       <c r="Q29">
-        <v>67.12089995000001</v>
+        <v>66.44945179999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1546453193624259</v>
+        <v>0.1558611964777345</v>
       </c>
       <c r="T29">
-        <v>1.052617426796043</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.205945126327437</v>
+        <v>4.055732800387171</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1243580614639688</v>
+        <v>0.1248817897933668</v>
       </c>
       <c r="C30">
-        <v>1237.945410064951</v>
+        <v>1213.189135690506</v>
       </c>
       <c r="D30">
-        <v>1399.337410064951</v>
+        <v>1390.070135690506</v>
       </c>
       <c r="E30">
-        <v>289.392</v>
+        <v>304.881</v>
       </c>
       <c r="F30">
-        <v>433.692</v>
+        <v>449.181</v>
       </c>
       <c r="G30">
         <v>272.3</v>
@@ -3747,45 +3747,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M30">
-        <v>25.0673976</v>
+        <v>27.5347953</v>
       </c>
       <c r="N30">
-        <v>76.59926906666666</v>
+        <v>74.13187136666667</v>
       </c>
       <c r="O30">
-        <v>19.14981726666667</v>
+        <v>18.53296784166667</v>
       </c>
       <c r="P30">
-        <v>57.4494518</v>
+        <v>55.598903525</v>
       </c>
       <c r="Q30">
-        <v>66.44945179999999</v>
+        <v>64.598903525</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1558611964777345</v>
+        <v>0.1571113236526293</v>
       </c>
       <c r="T30">
-        <v>1.064375887774551</v>
+        <v>1.076465573005974</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.055732800387171</v>
+        <v>3.692297892865275</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1248817897933668</v>
+        <v>0.1246705181227647</v>
       </c>
       <c r="C31">
-        <v>1213.189135690506</v>
+        <v>1201.423737954209</v>
       </c>
       <c r="D31">
-        <v>1390.070135690506</v>
+        <v>1393.793737954209</v>
       </c>
       <c r="E31">
-        <v>304.8809999999999</v>
+        <v>320.3699999999999</v>
       </c>
       <c r="F31">
-        <v>449.1809999999999</v>
+        <v>464.67</v>
       </c>
       <c r="G31">
         <v>272.3</v>
@@ -3829,28 +3829,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M31">
-        <v>27.5347953</v>
+        <v>28.484271</v>
       </c>
       <c r="N31">
-        <v>74.13187136666667</v>
+        <v>73.18239566666668</v>
       </c>
       <c r="O31">
-        <v>18.53296784166667</v>
+        <v>18.29559891666667</v>
       </c>
       <c r="P31">
-        <v>55.598903525</v>
+        <v>54.88679675000001</v>
       </c>
       <c r="Q31">
-        <v>64.598903525</v>
+        <v>63.88679675000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1571113236526293</v>
+        <v>0.1583971687468067</v>
       </c>
       <c r="T31">
-        <v>1.076465573005974</v>
+        <v>1.088900677815439</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.692297892865275</v>
+        <v>3.569221296436433</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1246705181227647</v>
+        <v>0.1251102464521626</v>
       </c>
       <c r="C32">
-        <v>1201.423737954209</v>
+        <v>1178.206977427257</v>
       </c>
       <c r="D32">
-        <v>1393.793737954209</v>
+        <v>1386.065977427257</v>
       </c>
       <c r="E32">
-        <v>320.3699999999999</v>
+        <v>335.8589999999999</v>
       </c>
       <c r="F32">
-        <v>464.67</v>
+        <v>480.1589999999999</v>
       </c>
       <c r="G32">
         <v>272.3</v>
@@ -3911,45 +3911,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M32">
-        <v>28.484271</v>
+        <v>30.7781919</v>
       </c>
       <c r="N32">
-        <v>73.18239566666668</v>
+        <v>70.88847476666668</v>
       </c>
       <c r="O32">
-        <v>18.29559891666667</v>
+        <v>17.72211869166667</v>
       </c>
       <c r="P32">
-        <v>54.88679675000001</v>
+        <v>53.16635607500001</v>
       </c>
       <c r="Q32">
-        <v>63.88679675000001</v>
+        <v>62.16635607500001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1583971687468067</v>
+        <v>0.1597202847132792</v>
       </c>
       <c r="T32">
-        <v>1.088900677815439</v>
+        <v>1.101696220445467</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.569221296436433</v>
+        <v>3.303204652079211</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1251102464521626</v>
+        <v>0.1249199747815606</v>
       </c>
       <c r="C33">
-        <v>1178.206977427257</v>
+        <v>1166.05125817991</v>
       </c>
       <c r="D33">
-        <v>1386.065977427257</v>
+        <v>1389.39925817991</v>
       </c>
       <c r="E33">
-        <v>335.8589999999999</v>
+        <v>351.348</v>
       </c>
       <c r="F33">
-        <v>480.1589999999999</v>
+        <v>495.648</v>
       </c>
       <c r="G33">
         <v>272.3</v>
@@ -3993,28 +3993,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M33">
-        <v>30.7781919</v>
+        <v>31.7710368</v>
       </c>
       <c r="N33">
-        <v>70.88847476666668</v>
+        <v>69.89562986666667</v>
       </c>
       <c r="O33">
-        <v>17.72211869166667</v>
+        <v>17.47390746666667</v>
       </c>
       <c r="P33">
-        <v>53.16635607500001</v>
+        <v>52.4217224</v>
       </c>
       <c r="Q33">
-        <v>62.16635607500001</v>
+        <v>61.4217224</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1597202847132792</v>
+        <v>0.1610823158552361</v>
       </c>
       <c r="T33">
-        <v>1.101696220445467</v>
+        <v>1.114868102564615</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.303204652079211</v>
+        <v>3.199979506701735</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1249199747815606</v>
+        <v>0.1247297031109585</v>
       </c>
       <c r="C34">
-        <v>1166.05125817991</v>
+        <v>1153.911609660626</v>
       </c>
       <c r="D34">
-        <v>1389.39925817991</v>
+        <v>1392.748609660626</v>
       </c>
       <c r="E34">
-        <v>351.348</v>
+        <v>366.837</v>
       </c>
       <c r="F34">
-        <v>495.648</v>
+        <v>511.137</v>
       </c>
       <c r="G34">
         <v>272.3</v>
@@ -4075,28 +4075,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M34">
-        <v>31.7710368</v>
+        <v>32.7638817</v>
       </c>
       <c r="N34">
-        <v>69.89562986666667</v>
+        <v>68.90278496666667</v>
       </c>
       <c r="O34">
-        <v>17.47390746666667</v>
+        <v>17.22569624166667</v>
       </c>
       <c r="P34">
-        <v>52.4217224</v>
+        <v>51.677088725</v>
       </c>
       <c r="Q34">
-        <v>61.4217224</v>
+        <v>60.677088725</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1610823158552361</v>
+        <v>0.1624850046432216</v>
       </c>
       <c r="T34">
-        <v>1.114868102564615</v>
+        <v>1.128433175194781</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.199979506701735</v>
+        <v>3.103010430741076</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1247297031109585</v>
+        <v>0.1245394314403564</v>
       </c>
       <c r="C35">
-        <v>1153.911609660626</v>
+        <v>1141.788148372822</v>
       </c>
       <c r="D35">
-        <v>1392.748609660626</v>
+        <v>1396.114148372822</v>
       </c>
       <c r="E35">
-        <v>366.837</v>
+        <v>382.326</v>
       </c>
       <c r="F35">
-        <v>511.137</v>
+        <v>526.626</v>
       </c>
       <c r="G35">
         <v>272.3</v>
@@ -4157,28 +4157,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M35">
-        <v>32.7638817</v>
+        <v>33.7567266</v>
       </c>
       <c r="N35">
-        <v>68.90278496666667</v>
+        <v>67.90994006666668</v>
       </c>
       <c r="O35">
-        <v>17.22569624166667</v>
+        <v>16.97748501666667</v>
       </c>
       <c r="P35">
-        <v>51.677088725</v>
+        <v>50.93245505000001</v>
       </c>
       <c r="Q35">
-        <v>60.677088725</v>
+        <v>59.93245505000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1624850046432216</v>
+        <v>0.1639301991520552</v>
       </c>
       <c r="T35">
-        <v>1.128433175194781</v>
+        <v>1.142409310631922</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.103010430741076</v>
+        <v>3.011745418072222</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1245394314403564</v>
+        <v>0.1263966597697544</v>
       </c>
       <c r="C36">
-        <v>1141.788148372822</v>
+        <v>1094.12780585269</v>
       </c>
       <c r="D36">
-        <v>1396.114148372822</v>
+        <v>1363.94280585269</v>
       </c>
       <c r="E36">
-        <v>382.326</v>
+        <v>397.815</v>
       </c>
       <c r="F36">
-        <v>526.626</v>
+        <v>542.115</v>
       </c>
       <c r="G36">
         <v>272.3</v>
@@ -4239,45 +4239,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M36">
-        <v>33.7567266</v>
+        <v>38.97806850000001</v>
       </c>
       <c r="N36">
-        <v>67.90994006666668</v>
+        <v>62.68859816666667</v>
       </c>
       <c r="O36">
-        <v>16.97748501666667</v>
+        <v>15.67214954166667</v>
       </c>
       <c r="P36">
-        <v>50.93245505000001</v>
+        <v>47.016448625</v>
       </c>
       <c r="Q36">
-        <v>59.93245505000001</v>
+        <v>56.016448625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1639301991520552</v>
+        <v>0.1654198611842375</v>
       </c>
       <c r="T36">
-        <v>1.142409310631922</v>
+        <v>1.156815481005591</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.011745418072222</v>
+        <v>2.608304376771944</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1263966597697544</v>
+        <v>0.1262648880991523</v>
       </c>
       <c r="C37">
-        <v>1094.12780585269</v>
+        <v>1080.872438762381</v>
       </c>
       <c r="D37">
-        <v>1363.94280585269</v>
+        <v>1366.176438762381</v>
       </c>
       <c r="E37">
-        <v>397.815</v>
+        <v>413.304</v>
       </c>
       <c r="F37">
-        <v>542.115</v>
+        <v>557.604</v>
       </c>
       <c r="G37">
         <v>272.3</v>
@@ -4321,28 +4321,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M37">
-        <v>38.97806850000001</v>
+        <v>40.09172760000001</v>
       </c>
       <c r="N37">
-        <v>62.68859816666667</v>
+        <v>61.57493906666667</v>
       </c>
       <c r="O37">
-        <v>15.67214954166667</v>
+        <v>15.39373476666667</v>
       </c>
       <c r="P37">
-        <v>47.016448625</v>
+        <v>46.1812043</v>
       </c>
       <c r="Q37">
-        <v>56.016448625</v>
+        <v>55.1812043</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1654198611842375</v>
+        <v>0.1669560751549255</v>
       </c>
       <c r="T37">
-        <v>1.156815481005591</v>
+        <v>1.171671844203437</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.608304376771944</v>
+        <v>2.535851477417168</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1262648880991523</v>
+        <v>0.1272153664285502</v>
       </c>
       <c r="C38">
-        <v>1080.872438762381</v>
+        <v>1049.434101970815</v>
       </c>
       <c r="D38">
-        <v>1366.176438762381</v>
+        <v>1350.227101970815</v>
       </c>
       <c r="E38">
-        <v>413.3039999999999</v>
+        <v>428.7929999999999</v>
       </c>
       <c r="F38">
-        <v>557.6039999999999</v>
+        <v>573.093</v>
       </c>
       <c r="G38">
         <v>272.3</v>
@@ -4403,45 +4403,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M38">
-        <v>40.0917276</v>
+        <v>43.4404494</v>
       </c>
       <c r="N38">
-        <v>61.57493906666667</v>
+        <v>58.22621726666667</v>
       </c>
       <c r="O38">
-        <v>15.39373476666667</v>
+        <v>14.55655431666667</v>
       </c>
       <c r="P38">
-        <v>46.1812043</v>
+        <v>43.66966295</v>
       </c>
       <c r="Q38">
-        <v>55.1812043</v>
+        <v>52.66966295</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1669560751549255</v>
+        <v>0.1685410578230956</v>
       </c>
       <c r="T38">
-        <v>1.171671844203437</v>
+        <v>1.186999837978992</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.535851477417169</v>
+        <v>2.340368667241888</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1272153664285502</v>
+        <v>0.1271128447579482</v>
       </c>
       <c r="C39">
-        <v>1049.434101970815</v>
+        <v>1035.647508750437</v>
       </c>
       <c r="D39">
-        <v>1350.227101970815</v>
+        <v>1351.929508750437</v>
       </c>
       <c r="E39">
-        <v>428.7929999999999</v>
+        <v>444.282</v>
       </c>
       <c r="F39">
-        <v>573.093</v>
+        <v>588.582</v>
       </c>
       <c r="G39">
         <v>272.3</v>
@@ -4485,28 +4485,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M39">
-        <v>43.4404494</v>
+        <v>44.6145156</v>
       </c>
       <c r="N39">
-        <v>58.22621726666667</v>
+        <v>57.05215106666667</v>
       </c>
       <c r="O39">
-        <v>14.55655431666667</v>
+        <v>14.26303776666667</v>
       </c>
       <c r="P39">
-        <v>43.66966295</v>
+        <v>42.7891133</v>
       </c>
       <c r="Q39">
-        <v>52.66966295</v>
+        <v>51.7891133</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1685410578230956</v>
+        <v>0.1701771689644325</v>
       </c>
       <c r="T39">
-        <v>1.186999837978992</v>
+        <v>1.202822283166662</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.340368667241888</v>
+        <v>2.278780018103943</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1271128447579482</v>
+        <v>0.1270103230873461</v>
       </c>
       <c r="C40">
-        <v>1035.647508750437</v>
+        <v>1021.865213840432</v>
       </c>
       <c r="D40">
-        <v>1351.929508750437</v>
+        <v>1353.636213840432</v>
       </c>
       <c r="E40">
-        <v>444.282</v>
+        <v>459.7709999999999</v>
       </c>
       <c r="F40">
-        <v>588.582</v>
+        <v>604.0709999999999</v>
       </c>
       <c r="G40">
         <v>272.3</v>
@@ -4567,28 +4567,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M40">
-        <v>44.6145156</v>
+        <v>45.7885818</v>
       </c>
       <c r="N40">
-        <v>57.05215106666667</v>
+        <v>55.87808486666668</v>
       </c>
       <c r="O40">
-        <v>14.26303776666667</v>
+        <v>13.96952121666667</v>
       </c>
       <c r="P40">
-        <v>42.7891133</v>
+        <v>41.90856365</v>
       </c>
       <c r="Q40">
-        <v>51.7891133</v>
+        <v>50.90856365</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1701771689644325</v>
+        <v>0.17186692309401</v>
       </c>
       <c r="T40">
-        <v>1.202822283166662</v>
+        <v>1.219163497049009</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.278780018103943</v>
+        <v>2.220349761229484</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1270103230873461</v>
+        <v>0.126907801416744</v>
       </c>
       <c r="C41">
-        <v>1021.865213840432</v>
+        <v>1008.087233540218</v>
       </c>
       <c r="D41">
-        <v>1353.636213840432</v>
+        <v>1355.347233540218</v>
       </c>
       <c r="E41">
-        <v>459.7709999999999</v>
+        <v>475.2599999999999</v>
       </c>
       <c r="F41">
-        <v>604.0709999999999</v>
+        <v>619.5599999999999</v>
       </c>
       <c r="G41">
         <v>272.3</v>
@@ -4649,28 +4649,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M41">
-        <v>45.7885818</v>
+        <v>46.962648</v>
       </c>
       <c r="N41">
-        <v>55.87808486666668</v>
+        <v>54.70401866666667</v>
       </c>
       <c r="O41">
-        <v>13.96952121666667</v>
+        <v>13.67600466666667</v>
       </c>
       <c r="P41">
-        <v>41.90856365</v>
+        <v>41.028014</v>
       </c>
       <c r="Q41">
-        <v>50.90856365</v>
+        <v>50.028014</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.17186692309401</v>
+        <v>0.1736130023612401</v>
       </c>
       <c r="T41">
-        <v>1.219163497049009</v>
+        <v>1.236049418060768</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.220349761229484</v>
+        <v>2.164841017198746</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.126907801416744</v>
+        <v>0.126805279746142</v>
       </c>
       <c r="C42">
-        <v>1008.087233540218</v>
+        <v>994.3135842317267</v>
       </c>
       <c r="D42">
-        <v>1355.347233540218</v>
+        <v>1357.062584231727</v>
       </c>
       <c r="E42">
-        <v>475.2599999999999</v>
+        <v>490.749</v>
       </c>
       <c r="F42">
-        <v>619.5599999999999</v>
+        <v>635.049</v>
       </c>
       <c r="G42">
         <v>272.3</v>
@@ -4731,28 +4731,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M42">
-        <v>46.962648</v>
+        <v>48.1367142</v>
       </c>
       <c r="N42">
-        <v>54.70401866666667</v>
+        <v>53.52995246666667</v>
       </c>
       <c r="O42">
-        <v>13.67600466666667</v>
+        <v>13.38248811666667</v>
       </c>
       <c r="P42">
-        <v>41.028014</v>
+        <v>40.14746435000001</v>
       </c>
       <c r="Q42">
-        <v>50.028014</v>
+        <v>49.14746435000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1736130023612401</v>
+        <v>0.1754182707561729</v>
       </c>
       <c r="T42">
-        <v>1.236049418060768</v>
+        <v>1.253507743174621</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.164841017198746</v>
+        <v>2.112040016779265</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.126805279746142</v>
+        <v>0.1267027580755399</v>
       </c>
       <c r="C43">
-        <v>994.3135842317267</v>
+        <v>980.5442823799297</v>
       </c>
       <c r="D43">
-        <v>1357.062584231727</v>
+        <v>1358.78228237993</v>
       </c>
       <c r="E43">
-        <v>490.749</v>
+        <v>506.238</v>
       </c>
       <c r="F43">
-        <v>635.049</v>
+        <v>650.538</v>
       </c>
       <c r="G43">
         <v>272.3</v>
@@ -4813,28 +4813,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M43">
-        <v>48.1367142</v>
+        <v>49.31078040000001</v>
       </c>
       <c r="N43">
-        <v>53.52995246666667</v>
+        <v>52.35588626666667</v>
       </c>
       <c r="O43">
-        <v>13.38248811666667</v>
+        <v>13.08897156666667</v>
       </c>
       <c r="P43">
-        <v>40.14746435000001</v>
+        <v>39.2669147</v>
       </c>
       <c r="Q43">
-        <v>49.14746435000001</v>
+        <v>48.2669147</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1754182707561729</v>
+        <v>0.1772857897854136</v>
       </c>
       <c r="T43">
-        <v>1.253507743174621</v>
+        <v>1.271568079499296</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.112040016779265</v>
+        <v>2.061753349713092</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1267027580755399</v>
+        <v>0.1266002364049378</v>
       </c>
       <c r="C44">
-        <v>980.5442823799298</v>
+        <v>966.7793445333615</v>
       </c>
       <c r="D44">
-        <v>1358.78228237993</v>
+        <v>1360.506344533361</v>
       </c>
       <c r="E44">
-        <v>506.2379999999999</v>
+        <v>521.7269999999999</v>
       </c>
       <c r="F44">
-        <v>650.5379999999999</v>
+        <v>666.0269999999999</v>
       </c>
       <c r="G44">
         <v>272.3</v>
@@ -4895,28 +4895,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M44">
-        <v>49.3107804</v>
+        <v>50.4848466</v>
       </c>
       <c r="N44">
-        <v>52.35588626666667</v>
+        <v>51.18182006666667</v>
       </c>
       <c r="O44">
-        <v>13.08897156666667</v>
+        <v>12.79545501666667</v>
       </c>
       <c r="P44">
-        <v>39.2669147</v>
+        <v>38.38636505000001</v>
       </c>
       <c r="Q44">
-        <v>48.2669147</v>
+        <v>47.38636505000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1772857897854136</v>
+        <v>0.1792188357981365</v>
       </c>
       <c r="T44">
-        <v>1.271568079499296</v>
+        <v>1.290262111835363</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.061753349713092</v>
+        <v>2.013805597394183</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1266002364049378</v>
+        <v>0.1311837147343358</v>
       </c>
       <c r="C45">
-        <v>966.7793445333615</v>
+        <v>878.257080911845</v>
       </c>
       <c r="D45">
-        <v>1360.506344533361</v>
+        <v>1287.473080911845</v>
       </c>
       <c r="E45">
-        <v>521.7269999999999</v>
+        <v>537.2159999999999</v>
       </c>
       <c r="F45">
-        <v>666.0269999999999</v>
+        <v>681.516</v>
       </c>
       <c r="G45">
         <v>272.3</v>
@@ -4977,45 +4977,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M45">
-        <v>50.4848466</v>
+        <v>61.33644</v>
       </c>
       <c r="N45">
-        <v>51.18182006666667</v>
+        <v>40.33022666666668</v>
       </c>
       <c r="O45">
-        <v>12.79545501666667</v>
+        <v>10.08255666666667</v>
       </c>
       <c r="P45">
-        <v>38.38636505000001</v>
+        <v>30.24767000000001</v>
       </c>
       <c r="Q45">
-        <v>47.38636505000001</v>
+        <v>39.24767000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1792188357981365</v>
+        <v>0.1812209191684568</v>
       </c>
       <c r="T45">
-        <v>1.290262111835363</v>
+        <v>1.309623788183433</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.013805597394183</v>
+        <v>1.657524738420858</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1311837147343358</v>
+        <v>0.1311876930637337</v>
       </c>
       <c r="C46">
-        <v>878.257080911845</v>
+        <v>862.7080957802287</v>
       </c>
       <c r="D46">
-        <v>1287.473080911845</v>
+        <v>1287.413095780229</v>
       </c>
       <c r="E46">
-        <v>537.2159999999999</v>
+        <v>552.7049999999999</v>
       </c>
       <c r="F46">
-        <v>681.516</v>
+        <v>697.005</v>
       </c>
       <c r="G46">
         <v>272.3</v>
@@ -5059,28 +5059,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M46">
-        <v>61.33644</v>
+        <v>62.73045</v>
       </c>
       <c r="N46">
-        <v>40.33022666666668</v>
+        <v>38.93621666666667</v>
       </c>
       <c r="O46">
-        <v>10.08255666666667</v>
+        <v>9.734054166666668</v>
       </c>
       <c r="P46">
-        <v>30.24767000000001</v>
+        <v>29.20216250000001</v>
       </c>
       <c r="Q46">
-        <v>39.24767000000001</v>
+        <v>38.20216250000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1812209191684568</v>
+        <v>0.1832958055704249</v>
       </c>
       <c r="T46">
-        <v>1.309623788183433</v>
+        <v>1.329689525489614</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.657524738420858</v>
+        <v>1.620690855344839</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1311876930637337</v>
+        <v>0.1311916713931316</v>
       </c>
       <c r="C47">
-        <v>862.7080957802287</v>
+        <v>847.1591162379309</v>
       </c>
       <c r="D47">
-        <v>1287.413095780229</v>
+        <v>1287.353116237931</v>
       </c>
       <c r="E47">
-        <v>552.7049999999999</v>
+        <v>568.194</v>
       </c>
       <c r="F47">
-        <v>697.005</v>
+        <v>712.4939999999999</v>
       </c>
       <c r="G47">
         <v>272.3</v>
@@ -5141,28 +5141,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M47">
-        <v>62.73045</v>
+        <v>64.12445999999998</v>
       </c>
       <c r="N47">
-        <v>38.93621666666667</v>
+        <v>37.54220666666669</v>
       </c>
       <c r="O47">
-        <v>9.734054166666668</v>
+        <v>9.385551666666672</v>
       </c>
       <c r="P47">
-        <v>29.20216250000001</v>
+        <v>28.15665500000001</v>
       </c>
       <c r="Q47">
-        <v>38.20216250000001</v>
+        <v>37.15665500000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1832958055704249</v>
+        <v>0.1854475396169104</v>
       </c>
       <c r="T47">
-        <v>1.329689525489614</v>
+        <v>1.35049843825158</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.620690855344839</v>
+        <v>1.585458445446039</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1311916713931316</v>
+        <v>0.1311956497225296</v>
       </c>
       <c r="C48">
-        <v>847.1591162379309</v>
+        <v>831.6101422841703</v>
       </c>
       <c r="D48">
-        <v>1287.353116237931</v>
+        <v>1287.29314228417</v>
       </c>
       <c r="E48">
-        <v>568.194</v>
+        <v>583.683</v>
       </c>
       <c r="F48">
-        <v>712.4939999999999</v>
+        <v>727.9829999999999</v>
       </c>
       <c r="G48">
         <v>272.3</v>
@@ -5223,28 +5223,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M48">
-        <v>64.12445999999998</v>
+        <v>65.51846999999999</v>
       </c>
       <c r="N48">
-        <v>37.54220666666669</v>
+        <v>36.14819666666668</v>
       </c>
       <c r="O48">
-        <v>9.385551666666672</v>
+        <v>9.037049166666669</v>
       </c>
       <c r="P48">
-        <v>28.15665500000001</v>
+        <v>27.11114750000001</v>
       </c>
       <c r="Q48">
-        <v>37.15665500000001</v>
+        <v>36.11114750000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1854475396169104</v>
+        <v>0.1876804711745841</v>
       </c>
       <c r="T48">
-        <v>1.35049843825158</v>
+        <v>1.372092593004564</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.585458445446039</v>
+        <v>1.551725287032293</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1311956497225296</v>
+        <v>0.1311996280519275</v>
       </c>
       <c r="C49">
-        <v>831.6101422841703</v>
+        <v>816.061173918165</v>
       </c>
       <c r="D49">
-        <v>1287.29314228417</v>
+        <v>1287.233173918165</v>
       </c>
       <c r="E49">
-        <v>583.683</v>
+        <v>599.172</v>
       </c>
       <c r="F49">
-        <v>727.9829999999999</v>
+        <v>743.472</v>
       </c>
       <c r="G49">
         <v>272.3</v>
@@ -5305,28 +5305,28 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M49">
-        <v>65.51846999999999</v>
+        <v>66.91248</v>
       </c>
       <c r="N49">
-        <v>36.14819666666668</v>
+        <v>34.75418666666667</v>
       </c>
       <c r="O49">
-        <v>9.037049166666669</v>
+        <v>8.688546666666667</v>
       </c>
       <c r="P49">
-        <v>27.11114750000001</v>
+        <v>26.06564</v>
       </c>
       <c r="Q49">
-        <v>36.11114750000001</v>
+        <v>35.06564</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1876804711745841</v>
+        <v>0.1899992847152452</v>
       </c>
       <c r="T49">
-        <v>1.372092593004564</v>
+        <v>1.394517292171123</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.551725287032293</v>
+        <v>1.519397676885787</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1311996280519275</v>
+        <v>0.1545644375823883</v>
       </c>
       <c r="C50">
-        <v>816.0611739181651</v>
+        <v>524.0483523601664</v>
       </c>
       <c r="D50">
-        <v>1287.233173918165</v>
+        <v>1010.709352360166</v>
       </c>
       <c r="E50">
-        <v>599.1719999999998</v>
+        <v>614.6609999999998</v>
       </c>
       <c r="F50">
-        <v>743.4719999999999</v>
+        <v>758.9609999999999</v>
       </c>
       <c r="G50">
         <v>272.3</v>
@@ -5387,45 +5387,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M50">
-        <v>66.91247999999999</v>
+        <v>111.4154748</v>
       </c>
       <c r="N50">
-        <v>34.75418666666668</v>
+        <v>-9.748808133333327</v>
       </c>
       <c r="O50">
-        <v>8.688546666666671</v>
+        <v>-2.437202033333332</v>
       </c>
       <c r="P50">
-        <v>26.06564000000001</v>
+        <v>-7.311606099999995</v>
       </c>
       <c r="Q50">
-        <v>35.06564000000002</v>
+        <v>1.688393900000005</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1899992847152452</v>
+        <v>0.1941998676328526</v>
       </c>
       <c r="T50">
-        <v>1.394517292171123</v>
+        <v>1.43514013941596</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.25</v>
+        <v>0.2281251030190527</v>
       </c>
       <c r="W50">
-        <v>0.0675</v>
+        <v>0.1133112348768031</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.519397676885787</v>
+        <v>0.9125004120762107</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1545644375823883</v>
+        <v>0.1555744375823883</v>
       </c>
       <c r="C51">
-        <v>524.0483523601664</v>
+        <v>499.2601341781771</v>
       </c>
       <c r="D51">
-        <v>1010.709352360166</v>
+        <v>1001.410134178177</v>
       </c>
       <c r="E51">
-        <v>614.6609999999998</v>
+        <v>630.1499999999999</v>
       </c>
       <c r="F51">
-        <v>758.9609999999999</v>
+        <v>774.4499999999999</v>
       </c>
       <c r="G51">
         <v>272.3</v>
@@ -5469,37 +5469,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M51">
-        <v>111.4154748</v>
+        <v>113.68926</v>
       </c>
       <c r="N51">
-        <v>-9.748808133333327</v>
+        <v>-12.02259333333333</v>
       </c>
       <c r="O51">
-        <v>-2.437202033333332</v>
+        <v>-3.005648333333333</v>
       </c>
       <c r="P51">
-        <v>-7.311606099999995</v>
+        <v>-9.016945</v>
       </c>
       <c r="Q51">
-        <v>1.688393900000005</v>
+        <v>-0.01694499999999977</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1941998676328526</v>
+        <v>0.1971678649855096</v>
       </c>
       <c r="T51">
-        <v>1.43514013941596</v>
+        <v>1.463842942204279</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2281251030190527</v>
+        <v>0.2235626009586716</v>
       </c>
       <c r="W51">
-        <v>0.1133112348768031</v>
+        <v>0.113981010179267</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9125004120762107</v>
+        <v>0.8942504038346865</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1555744375823883</v>
+        <v>0.1565844375823883</v>
       </c>
       <c r="C52">
-        <v>499.2601341781771</v>
+        <v>474.6414742946055</v>
       </c>
       <c r="D52">
-        <v>1001.410134178177</v>
+        <v>992.2804742946055</v>
       </c>
       <c r="E52">
-        <v>630.1499999999999</v>
+        <v>645.6389999999999</v>
       </c>
       <c r="F52">
-        <v>774.4499999999999</v>
+        <v>789.939</v>
       </c>
       <c r="G52">
         <v>272.3</v>
@@ -5551,37 +5551,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M52">
-        <v>113.68926</v>
+        <v>115.9630452</v>
       </c>
       <c r="N52">
-        <v>-12.02259333333333</v>
+        <v>-14.29637853333334</v>
       </c>
       <c r="O52">
-        <v>-3.005648333333333</v>
+        <v>-3.574094633333335</v>
       </c>
       <c r="P52">
-        <v>-9.016945</v>
+        <v>-10.7222839</v>
       </c>
       <c r="Q52">
-        <v>-0.01694499999999977</v>
+        <v>-1.722283900000004</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1971678649855096</v>
+        <v>0.2002570050872547</v>
       </c>
       <c r="T52">
-        <v>1.463842942204279</v>
+        <v>1.49371728796355</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2235626009586716</v>
+        <v>0.2191790205477173</v>
       </c>
       <c r="W52">
-        <v>0.113981010179267</v>
+        <v>0.1146245197835951</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8942504038346865</v>
+        <v>0.8767160821908691</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1565844375823883</v>
+        <v>0.1575944375823883</v>
       </c>
       <c r="C53">
-        <v>474.6414742946055</v>
+        <v>450.187777117262</v>
       </c>
       <c r="D53">
-        <v>992.2804742946055</v>
+        <v>983.315777117262</v>
       </c>
       <c r="E53">
-        <v>645.6389999999999</v>
+        <v>661.1279999999999</v>
       </c>
       <c r="F53">
-        <v>789.939</v>
+        <v>805.428</v>
       </c>
       <c r="G53">
         <v>272.3</v>
@@ -5633,37 +5633,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M53">
-        <v>115.9630452</v>
+        <v>118.2368304</v>
       </c>
       <c r="N53">
-        <v>-14.29637853333334</v>
+        <v>-16.57016373333335</v>
       </c>
       <c r="O53">
-        <v>-3.574094633333335</v>
+        <v>-4.142540933333336</v>
       </c>
       <c r="P53">
-        <v>-10.7222839</v>
+        <v>-12.42762280000001</v>
       </c>
       <c r="Q53">
-        <v>-1.722283900000004</v>
+        <v>-3.427622800000009</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2002570050872547</v>
+        <v>0.2034748593599059</v>
       </c>
       <c r="T53">
-        <v>1.49371728796355</v>
+        <v>1.524836398129458</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2191790205477173</v>
+        <v>0.2149640393833381</v>
       </c>
       <c r="W53">
-        <v>0.1146245197835951</v>
+        <v>0.115243279018526</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8767160821908691</v>
+        <v>0.8598561575333523</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1575944375823883</v>
+        <v>0.1586044375823883</v>
       </c>
       <c r="C54">
-        <v>450.187777117262</v>
+        <v>425.8946116413863</v>
       </c>
       <c r="D54">
-        <v>983.315777117262</v>
+        <v>974.5116116413863</v>
       </c>
       <c r="E54">
-        <v>661.1279999999999</v>
+        <v>676.617</v>
       </c>
       <c r="F54">
-        <v>805.428</v>
+        <v>820.9169999999999</v>
       </c>
       <c r="G54">
         <v>272.3</v>
@@ -5715,37 +5715,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M54">
-        <v>118.2368304</v>
+        <v>120.5106156</v>
       </c>
       <c r="N54">
-        <v>-16.57016373333335</v>
+        <v>-18.84394893333332</v>
       </c>
       <c r="O54">
-        <v>-4.142540933333336</v>
+        <v>-4.710987233333331</v>
       </c>
       <c r="P54">
-        <v>-12.42762280000001</v>
+        <v>-14.13296169999999</v>
       </c>
       <c r="Q54">
-        <v>-3.427622800000009</v>
+        <v>-5.132961699999992</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2034748593599059</v>
+        <v>0.206829643601606</v>
       </c>
       <c r="T54">
-        <v>1.524836398129458</v>
+        <v>1.557279725749233</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2149640393833381</v>
+        <v>0.2109081141119544</v>
       </c>
       <c r="W54">
-        <v>0.115243279018526</v>
+        <v>0.1158386888483651</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8598561575333523</v>
+        <v>0.8436324564478175</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1586044375823883</v>
+        <v>0.1596144375823883</v>
       </c>
       <c r="C55">
-        <v>425.8946116413863</v>
+        <v>401.7577041468271</v>
       </c>
       <c r="D55">
-        <v>974.5116116413863</v>
+        <v>965.863704146827</v>
       </c>
       <c r="E55">
-        <v>676.617</v>
+        <v>692.106</v>
       </c>
       <c r="F55">
-        <v>820.9169999999999</v>
+        <v>836.4059999999999</v>
       </c>
       <c r="G55">
         <v>272.3</v>
@@ -5797,37 +5797,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M55">
-        <v>120.5106156</v>
+        <v>122.7844008</v>
       </c>
       <c r="N55">
-        <v>-18.84394893333332</v>
+        <v>-21.11773413333333</v>
       </c>
       <c r="O55">
-        <v>-4.710987233333331</v>
+        <v>-5.279433533333332</v>
       </c>
       <c r="P55">
-        <v>-14.13296169999999</v>
+        <v>-15.8383006</v>
       </c>
       <c r="Q55">
-        <v>-5.132961699999992</v>
+        <v>-6.838300599999997</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.206829643601606</v>
+        <v>0.2103302880277279</v>
       </c>
       <c r="T55">
-        <v>1.557279725749233</v>
+        <v>1.591133632830738</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2109081141119544</v>
+        <v>0.2070024082950663</v>
       </c>
       <c r="W55">
-        <v>0.1158386888483651</v>
+        <v>0.1164120464622843</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8436324564478175</v>
+        <v>0.8280096331802653</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1596144375823883</v>
+        <v>0.1606244375823883</v>
       </c>
       <c r="C56">
-        <v>401.7577041468271</v>
+        <v>377.7729312806339</v>
       </c>
       <c r="D56">
-        <v>965.863704146827</v>
+        <v>957.3679312806339</v>
       </c>
       <c r="E56">
-        <v>692.106</v>
+        <v>707.595</v>
       </c>
       <c r="F56">
-        <v>836.4059999999999</v>
+        <v>851.895</v>
       </c>
       <c r="G56">
         <v>272.3</v>
@@ -5879,37 +5879,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M56">
-        <v>122.7844008</v>
+        <v>125.058186</v>
       </c>
       <c r="N56">
-        <v>-21.11773413333333</v>
+        <v>-23.39151933333333</v>
       </c>
       <c r="O56">
-        <v>-5.279433533333332</v>
+        <v>-5.847879833333334</v>
       </c>
       <c r="P56">
-        <v>-15.8383006</v>
+        <v>-17.5436395</v>
       </c>
       <c r="Q56">
-        <v>-6.838300599999997</v>
+        <v>-8.543639500000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2103302880277279</v>
+        <v>0.2139865166505663</v>
       </c>
       <c r="T56">
-        <v>1.591133632830738</v>
+        <v>1.626492158004755</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2070024082950663</v>
+        <v>0.2032387281442469</v>
       </c>
       <c r="W56">
-        <v>0.1164120464622843</v>
+        <v>0.1169645547084246</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8280096331802653</v>
+        <v>0.8129549125769877</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1606244375823883</v>
+        <v>0.1944358705026865</v>
       </c>
       <c r="C57">
-        <v>377.7729312806339</v>
+        <v>144.5035161018179</v>
       </c>
       <c r="D57">
-        <v>957.3679312806339</v>
+        <v>739.5875161018179</v>
       </c>
       <c r="E57">
-        <v>707.595</v>
+        <v>723.0840000000001</v>
       </c>
       <c r="F57">
-        <v>851.895</v>
+        <v>867.384</v>
       </c>
       <c r="G57">
         <v>272.3</v>
@@ -5961,45 +5961,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M57">
-        <v>125.058186</v>
+        <v>174.1707072</v>
       </c>
       <c r="N57">
-        <v>-23.39151933333333</v>
+        <v>-72.50404053333334</v>
       </c>
       <c r="O57">
-        <v>-5.847879833333334</v>
+        <v>-18.12601013333333</v>
       </c>
       <c r="P57">
-        <v>-17.5436395</v>
+        <v>-54.3780304</v>
       </c>
       <c r="Q57">
-        <v>-8.543639500000001</v>
+        <v>-45.3780304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2139865166505663</v>
+        <v>0.2236303759387569</v>
       </c>
       <c r="T57">
-        <v>1.626492158004755</v>
+        <v>1.719755647953434</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.2032387281442469</v>
+        <v>0.145929628898393</v>
       </c>
       <c r="W57">
-        <v>0.1169645547084246</v>
+        <v>0.1714973305172027</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8129549125769877</v>
+        <v>0.583718515593572</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1944358705026865</v>
+        <v>0.1959858705026866</v>
       </c>
       <c r="C58">
-        <v>144.5035161018179</v>
+        <v>121.3815700322516</v>
       </c>
       <c r="D58">
-        <v>739.5875161018179</v>
+        <v>731.9545700322517</v>
       </c>
       <c r="E58">
-        <v>723.0840000000001</v>
+        <v>738.5730000000001</v>
       </c>
       <c r="F58">
-        <v>867.384</v>
+        <v>882.873</v>
       </c>
       <c r="G58">
         <v>272.3</v>
@@ -6043,37 +6043,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M58">
-        <v>174.1707072</v>
+        <v>177.2808984</v>
       </c>
       <c r="N58">
-        <v>-72.50404053333334</v>
+        <v>-75.61423173333334</v>
       </c>
       <c r="O58">
-        <v>-18.12601013333333</v>
+        <v>-18.90355793333334</v>
       </c>
       <c r="P58">
-        <v>-54.3780304</v>
+        <v>-56.71067380000001</v>
       </c>
       <c r="Q58">
-        <v>-45.3780304</v>
+        <v>-47.71067380000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2236303759387569</v>
+        <v>0.2277659660768676</v>
       </c>
       <c r="T58">
-        <v>1.719755647953434</v>
+        <v>1.7597499653477</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.145929628898393</v>
+        <v>0.143369459970351</v>
       </c>
       <c r="W58">
-        <v>0.1714973305172027</v>
+        <v>0.1720114124379535</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.583718515593572</v>
+        <v>0.573477839881404</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1959858705026866</v>
+        <v>0.1975358705026866</v>
       </c>
       <c r="C59">
-        <v>121.3815700322516</v>
+        <v>98.41556687016873</v>
       </c>
       <c r="D59">
-        <v>731.9545700322517</v>
+        <v>724.4775668701689</v>
       </c>
       <c r="E59">
-        <v>738.5730000000001</v>
+        <v>754.0620000000001</v>
       </c>
       <c r="F59">
-        <v>882.873</v>
+        <v>898.3620000000001</v>
       </c>
       <c r="G59">
         <v>272.3</v>
@@ -6125,37 +6125,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M59">
-        <v>177.2808984</v>
+        <v>180.3910896</v>
       </c>
       <c r="N59">
-        <v>-75.61423173333334</v>
+        <v>-78.72442293333334</v>
       </c>
       <c r="O59">
-        <v>-18.90355793333334</v>
+        <v>-19.68110573333334</v>
       </c>
       <c r="P59">
-        <v>-56.71067380000001</v>
+        <v>-59.0433172</v>
       </c>
       <c r="Q59">
-        <v>-47.71067380000001</v>
+        <v>-50.0433172</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2277659660768676</v>
+        <v>0.2320984890786977</v>
       </c>
       <c r="T59">
-        <v>1.7597499653477</v>
+        <v>1.801648774046455</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.143369459970351</v>
+        <v>0.1408975727294829</v>
       </c>
       <c r="W59">
-        <v>0.1720114124379535</v>
+        <v>0.1725077673959198</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.573477839881404</v>
+        <v>0.5635902909179316</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1975358705026866</v>
+        <v>0.1990858705026866</v>
       </c>
       <c r="C60">
-        <v>98.41556687016896</v>
+        <v>75.6007760130849</v>
       </c>
       <c r="D60">
-        <v>724.4775668701689</v>
+        <v>717.1517760130848</v>
       </c>
       <c r="E60">
-        <v>754.0619999999999</v>
+        <v>769.5509999999999</v>
       </c>
       <c r="F60">
-        <v>898.3619999999999</v>
+        <v>913.8509999999999</v>
       </c>
       <c r="G60">
         <v>272.3</v>
@@ -6207,37 +6207,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M60">
-        <v>180.3910896</v>
+        <v>183.5012808</v>
       </c>
       <c r="N60">
-        <v>-78.72442293333332</v>
+        <v>-81.83461413333332</v>
       </c>
       <c r="O60">
-        <v>-19.68110573333333</v>
+        <v>-20.45865353333333</v>
       </c>
       <c r="P60">
-        <v>-59.04331719999999</v>
+        <v>-61.37596059999998</v>
       </c>
       <c r="Q60">
-        <v>-50.04331719999999</v>
+        <v>-52.37596059999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2320984890786977</v>
+        <v>0.236642354665983</v>
       </c>
       <c r="T60">
-        <v>1.801648774046454</v>
+        <v>1.845591427071978</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1408975727294829</v>
+        <v>0.1385094782764408</v>
       </c>
       <c r="W60">
-        <v>0.1725077673959198</v>
+        <v>0.1729872967620907</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5635902909179317</v>
+        <v>0.5540379131057633</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1990858705026866</v>
+        <v>0.2006358705026866</v>
       </c>
       <c r="C61">
-        <v>75.6007760130849</v>
+        <v>52.93265628319659</v>
       </c>
       <c r="D61">
-        <v>717.1517760130848</v>
+        <v>709.9726562831964</v>
       </c>
       <c r="E61">
-        <v>769.5509999999999</v>
+        <v>785.04</v>
       </c>
       <c r="F61">
-        <v>913.8509999999999</v>
+        <v>929.3399999999999</v>
       </c>
       <c r="G61">
         <v>272.3</v>
@@ -6289,37 +6289,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M61">
-        <v>183.5012808</v>
+        <v>186.611472</v>
       </c>
       <c r="N61">
-        <v>-81.83461413333332</v>
+        <v>-84.94480533333332</v>
       </c>
       <c r="O61">
-        <v>-20.45865353333333</v>
+        <v>-21.23620133333333</v>
       </c>
       <c r="P61">
-        <v>-61.37596059999998</v>
+        <v>-63.70860399999999</v>
       </c>
       <c r="Q61">
-        <v>-52.37596059999998</v>
+        <v>-54.70860399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.236642354665983</v>
+        <v>0.2414134135326326</v>
       </c>
       <c r="T61">
-        <v>1.845591427071978</v>
+        <v>1.891731212748777</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1385094782764408</v>
+        <v>0.1362009869718335</v>
       </c>
       <c r="W61">
-        <v>0.1729872967620907</v>
+        <v>0.1734508418160559</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5540379131057633</v>
+        <v>0.5448039478873339</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2006358705026866</v>
+        <v>0.2021858705026865</v>
       </c>
       <c r="C62">
-        <v>52.93265628319659</v>
+        <v>30.40684654008078</v>
       </c>
       <c r="D62">
-        <v>709.9726562831964</v>
+        <v>702.9358465400807</v>
       </c>
       <c r="E62">
-        <v>785.04</v>
+        <v>800.529</v>
       </c>
       <c r="F62">
-        <v>929.3399999999999</v>
+        <v>944.829</v>
       </c>
       <c r="G62">
         <v>272.3</v>
@@ -6371,37 +6371,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M62">
-        <v>186.611472</v>
+        <v>189.7216632</v>
       </c>
       <c r="N62">
-        <v>-84.94480533333332</v>
+        <v>-88.05499653333332</v>
       </c>
       <c r="O62">
-        <v>-21.23620133333333</v>
+        <v>-22.01374913333333</v>
       </c>
       <c r="P62">
-        <v>-63.70860399999999</v>
+        <v>-66.04124739999999</v>
       </c>
       <c r="Q62">
-        <v>-54.70860399999999</v>
+        <v>-57.04124739999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2414134135326326</v>
+        <v>0.2464291420847514</v>
       </c>
       <c r="T62">
-        <v>1.891731212748777</v>
+        <v>1.940237141280797</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1362009869718335</v>
+        <v>0.1339681839067215</v>
       </c>
       <c r="W62">
-        <v>0.1734508418160559</v>
+        <v>0.1738991886715303</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5448039478873339</v>
+        <v>0.5358727356268858</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2021858705026865</v>
+        <v>0.2037358705026865</v>
       </c>
       <c r="C63">
-        <v>30.40684654008078</v>
+        <v>8.019156846161309</v>
       </c>
       <c r="D63">
-        <v>702.9358465400807</v>
+        <v>696.0371568461611</v>
       </c>
       <c r="E63">
-        <v>800.529</v>
+        <v>816.0179999999998</v>
       </c>
       <c r="F63">
-        <v>944.829</v>
+        <v>960.3179999999999</v>
       </c>
       <c r="G63">
         <v>272.3</v>
@@ -6453,37 +6453,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M63">
-        <v>189.7216632</v>
+        <v>192.8318544</v>
       </c>
       <c r="N63">
-        <v>-88.05499653333332</v>
+        <v>-91.1651877333333</v>
       </c>
       <c r="O63">
-        <v>-22.01374913333333</v>
+        <v>-22.79129693333332</v>
       </c>
       <c r="P63">
-        <v>-66.04124739999999</v>
+        <v>-68.37389079999997</v>
       </c>
       <c r="Q63">
-        <v>-57.04124739999999</v>
+        <v>-59.37389079999997</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2464291420847514</v>
+        <v>0.2517088563501395</v>
       </c>
       <c r="T63">
-        <v>1.940237141280797</v>
+        <v>1.991296013419765</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1339681839067215</v>
+        <v>0.1318074067469356</v>
       </c>
       <c r="W63">
-        <v>0.1738991886715303</v>
+        <v>0.1743330727252153</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5358727356268858</v>
+        <v>0.5272296269877426</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2037358705026865</v>
+        <v>0.2052858705026865</v>
       </c>
       <c r="C64">
-        <v>8.019156846161309</v>
+        <v>-14.23443985266306</v>
       </c>
       <c r="D64">
-        <v>696.0371568461611</v>
+        <v>689.2725601473369</v>
       </c>
       <c r="E64">
-        <v>816.0179999999998</v>
+        <v>831.5069999999998</v>
       </c>
       <c r="F64">
-        <v>960.3179999999999</v>
+        <v>975.8069999999999</v>
       </c>
       <c r="G64">
         <v>272.3</v>
@@ -6535,37 +6535,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M64">
-        <v>192.8318544</v>
+        <v>195.9420456</v>
       </c>
       <c r="N64">
-        <v>-91.1651877333333</v>
+        <v>-94.27537893333333</v>
       </c>
       <c r="O64">
-        <v>-22.79129693333332</v>
+        <v>-23.56884473333333</v>
       </c>
       <c r="P64">
-        <v>-68.37389079999997</v>
+        <v>-70.70653419999999</v>
       </c>
       <c r="Q64">
-        <v>-59.37389079999997</v>
+        <v>-61.70653419999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2517088563501395</v>
+        <v>0.257273960575819</v>
       </c>
       <c r="T64">
-        <v>1.991296013419765</v>
+        <v>2.045114824593272</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1318074067469356</v>
+        <v>0.1297152256874605</v>
       </c>
       <c r="W64">
-        <v>0.1743330727252153</v>
+        <v>0.1747531826819579</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5272296269877426</v>
+        <v>0.5188609027498419</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2052858705026865</v>
+        <v>0.2068358705026865</v>
       </c>
       <c r="C65">
-        <v>-14.23443985266306</v>
+        <v>-36.35781556593349</v>
       </c>
       <c r="D65">
-        <v>689.2725601473369</v>
+        <v>682.6381844340665</v>
       </c>
       <c r="E65">
-        <v>831.5069999999998</v>
+        <v>846.9959999999999</v>
       </c>
       <c r="F65">
-        <v>975.8069999999999</v>
+        <v>991.2959999999999</v>
       </c>
       <c r="G65">
         <v>272.3</v>
@@ -6617,37 +6617,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M65">
-        <v>195.9420456</v>
+        <v>199.0522368</v>
       </c>
       <c r="N65">
-        <v>-94.27537893333333</v>
+        <v>-97.38557013333333</v>
       </c>
       <c r="O65">
-        <v>-23.56884473333333</v>
+        <v>-24.34639253333333</v>
       </c>
       <c r="P65">
-        <v>-70.70653419999999</v>
+        <v>-73.0391776</v>
       </c>
       <c r="Q65">
-        <v>-61.70653419999999</v>
+        <v>-64.0391776</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.257273960575819</v>
+        <v>0.2631482372584806</v>
       </c>
       <c r="T65">
-        <v>2.045114824593272</v>
+        <v>2.101923569720863</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1297152256874605</v>
+        <v>0.1276884252860939</v>
       </c>
       <c r="W65">
-        <v>0.1747531826819579</v>
+        <v>0.1751601642025523</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5188609027498419</v>
+        <v>0.5107537011443755</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2068358705026865</v>
+        <v>0.2083858705026865</v>
       </c>
       <c r="C66">
-        <v>-36.35781556593349</v>
+        <v>-58.35469464916116</v>
       </c>
       <c r="D66">
-        <v>682.6381844340665</v>
+        <v>676.1303053508389</v>
       </c>
       <c r="E66">
-        <v>846.9959999999999</v>
+        <v>862.4849999999999</v>
       </c>
       <c r="F66">
-        <v>991.2959999999999</v>
+        <v>1006.785</v>
       </c>
       <c r="G66">
         <v>272.3</v>
@@ -6699,37 +6699,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M66">
-        <v>199.0522368</v>
+        <v>202.162428</v>
       </c>
       <c r="N66">
-        <v>-97.38557013333333</v>
+        <v>-100.4957613333333</v>
       </c>
       <c r="O66">
-        <v>-24.34639253333333</v>
+        <v>-25.12394033333333</v>
       </c>
       <c r="P66">
-        <v>-73.0391776</v>
+        <v>-75.371821</v>
       </c>
       <c r="Q66">
-        <v>-64.0391776</v>
+        <v>-66.371821</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2631482372584806</v>
+        <v>0.2693581868944372</v>
       </c>
       <c r="T66">
-        <v>2.101923569720863</v>
+        <v>2.161978528855745</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1276884252860939</v>
+        <v>0.1257239879740001</v>
       </c>
       <c r="W66">
-        <v>0.1751601642025523</v>
+        <v>0.1755546232148208</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5107537011443755</v>
+        <v>0.5028959518960006</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2083858705026865</v>
+        <v>0.2340694396247056</v>
       </c>
       <c r="C67">
-        <v>-58.35469464916116</v>
+        <v>-166.0808599989183</v>
       </c>
       <c r="D67">
-        <v>676.1303053508389</v>
+        <v>583.8931400010816</v>
       </c>
       <c r="E67">
-        <v>862.4849999999999</v>
+        <v>877.9739999999999</v>
       </c>
       <c r="F67">
-        <v>1006.785</v>
+        <v>1022.274</v>
       </c>
       <c r="G67">
         <v>272.3</v>
@@ -6781,45 +6781,45 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M67">
-        <v>202.162428</v>
+        <v>241.0522092</v>
       </c>
       <c r="N67">
-        <v>-100.4957613333333</v>
+        <v>-139.3855425333334</v>
       </c>
       <c r="O67">
-        <v>-25.12394033333333</v>
+        <v>-34.84638563333334</v>
       </c>
       <c r="P67">
-        <v>-75.371821</v>
+        <v>-104.5391569</v>
       </c>
       <c r="Q67">
-        <v>-66.371821</v>
+        <v>-95.53915690000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2693581868944372</v>
+        <v>0.2789733368678589</v>
       </c>
       <c r="T67">
-        <v>2.161978528855745</v>
+        <v>2.254964377788584</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1257239879740001</v>
+        <v>0.1054405049886042</v>
       </c>
       <c r="W67">
-        <v>0.1755546232148208</v>
+        <v>0.2109371289236871</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5028959518960006</v>
+        <v>0.4217620199544168</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2340694396247056</v>
+        <v>0.2359694396247055</v>
       </c>
       <c r="C68">
-        <v>-166.0808599989183</v>
+        <v>-187.4035889523789</v>
       </c>
       <c r="D68">
-        <v>583.8931400010816</v>
+        <v>578.059411047621</v>
       </c>
       <c r="E68">
-        <v>877.9739999999999</v>
+        <v>893.463</v>
       </c>
       <c r="F68">
-        <v>1022.274</v>
+        <v>1037.763</v>
       </c>
       <c r="G68">
         <v>272.3</v>
@@ -6863,37 +6863,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M68">
-        <v>241.0522092</v>
+        <v>244.7045154</v>
       </c>
       <c r="N68">
-        <v>-139.3855425333334</v>
+        <v>-143.0378487333333</v>
       </c>
       <c r="O68">
-        <v>-34.84638563333334</v>
+        <v>-35.75946218333333</v>
       </c>
       <c r="P68">
-        <v>-104.5391569</v>
+        <v>-107.27838655</v>
       </c>
       <c r="Q68">
-        <v>-95.53915690000002</v>
+        <v>-98.27838654999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2789733368678589</v>
+        <v>0.2860391955608244</v>
       </c>
       <c r="T68">
-        <v>2.254964377788584</v>
+        <v>2.323296631660966</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1054405049886042</v>
+        <v>0.1038667661081773</v>
       </c>
       <c r="W68">
-        <v>0.2109371289236871</v>
+        <v>0.2113082165516918</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4217620199544168</v>
+        <v>0.4154670644327092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2359694396247055</v>
+        <v>0.2378694396247055</v>
       </c>
       <c r="C69">
-        <v>-187.4035889523789</v>
+        <v>-208.6109004293976</v>
       </c>
       <c r="D69">
-        <v>578.059411047621</v>
+        <v>572.3410995706024</v>
       </c>
       <c r="E69">
-        <v>893.463</v>
+        <v>908.952</v>
       </c>
       <c r="F69">
-        <v>1037.763</v>
+        <v>1053.252</v>
       </c>
       <c r="G69">
         <v>272.3</v>
@@ -6945,37 +6945,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M69">
-        <v>244.7045154</v>
+        <v>248.3568216</v>
       </c>
       <c r="N69">
-        <v>-143.0378487333333</v>
+        <v>-146.6901549333333</v>
       </c>
       <c r="O69">
-        <v>-35.75946218333333</v>
+        <v>-36.67253873333333</v>
       </c>
       <c r="P69">
-        <v>-107.27838655</v>
+        <v>-110.0176162</v>
       </c>
       <c r="Q69">
-        <v>-98.27838654999998</v>
+        <v>-101.0176162</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2860391955608244</v>
+        <v>0.2935466704221001</v>
       </c>
       <c r="T69">
-        <v>2.323296631660966</v>
+        <v>2.395899651400371</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1038667661081773</v>
+        <v>0.10233931366541</v>
       </c>
       <c r="W69">
-        <v>0.2113082165516918</v>
+        <v>0.2116683898376963</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4154670644327092</v>
+        <v>0.40935725466164</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2378694396247055</v>
+        <v>0.2397694396247055</v>
       </c>
       <c r="C70">
-        <v>-208.6109004293976</v>
+        <v>-229.7061860962951</v>
       </c>
       <c r="D70">
-        <v>572.3410995706024</v>
+        <v>566.7348139037048</v>
       </c>
       <c r="E70">
-        <v>908.952</v>
+        <v>924.441</v>
       </c>
       <c r="F70">
-        <v>1053.252</v>
+        <v>1068.741</v>
       </c>
       <c r="G70">
         <v>272.3</v>
@@ -7027,37 +7027,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M70">
-        <v>248.3568216</v>
+        <v>252.0091278</v>
       </c>
       <c r="N70">
-        <v>-146.6901549333333</v>
+        <v>-150.3424611333334</v>
       </c>
       <c r="O70">
-        <v>-36.67253873333333</v>
+        <v>-37.58561528333334</v>
       </c>
       <c r="P70">
-        <v>-110.0176162</v>
+        <v>-112.75684585</v>
       </c>
       <c r="Q70">
-        <v>-101.0176162</v>
+        <v>-103.75684585</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2935466704221001</v>
+        <v>0.3015384985002324</v>
       </c>
       <c r="T70">
-        <v>2.395899651400371</v>
+        <v>2.473186736929415</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.10233931366541</v>
+        <v>0.100856135206491</v>
       </c>
       <c r="W70">
-        <v>0.2116683898376963</v>
+        <v>0.2120181233183094</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.40935725466164</v>
+        <v>0.4034245408259639</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2397694396247055</v>
+        <v>0.2416694396247056</v>
       </c>
       <c r="C71">
-        <v>-229.7061860962951</v>
+        <v>-250.6927060181383</v>
       </c>
       <c r="D71">
-        <v>566.7348139037048</v>
+        <v>561.2372939818617</v>
       </c>
       <c r="E71">
-        <v>924.441</v>
+        <v>939.9300000000001</v>
       </c>
       <c r="F71">
-        <v>1068.741</v>
+        <v>1084.23</v>
       </c>
       <c r="G71">
         <v>272.3</v>
@@ -7109,37 +7109,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M71">
-        <v>252.0091278</v>
+        <v>255.661434</v>
       </c>
       <c r="N71">
-        <v>-150.3424611333334</v>
+        <v>-153.9947673333334</v>
       </c>
       <c r="O71">
-        <v>-37.58561528333334</v>
+        <v>-38.49869183333334</v>
       </c>
       <c r="P71">
-        <v>-112.75684585</v>
+        <v>-115.4960755</v>
       </c>
       <c r="Q71">
-        <v>-103.75684585</v>
+        <v>-106.4960755</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3015384985002324</v>
+        <v>0.3100631151169068</v>
       </c>
       <c r="T71">
-        <v>2.473186736929415</v>
+        <v>2.555626294827062</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.100856135206491</v>
+        <v>0.09941533327496968</v>
       </c>
       <c r="W71">
-        <v>0.2120181233183094</v>
+        <v>0.2123578644137622</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4034245408259639</v>
+        <v>0.3976613330998787</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2416694396247056</v>
+        <v>0.2435694396247056</v>
       </c>
       <c r="C72">
-        <v>-250.6927060181383</v>
+        <v>-271.5735949803011</v>
       </c>
       <c r="D72">
-        <v>561.2372939818617</v>
+        <v>555.845405019699</v>
       </c>
       <c r="E72">
-        <v>939.9300000000001</v>
+        <v>955.4190000000001</v>
       </c>
       <c r="F72">
-        <v>1084.23</v>
+        <v>1099.719</v>
       </c>
       <c r="G72">
         <v>272.3</v>
@@ -7191,37 +7191,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M72">
-        <v>255.661434</v>
+        <v>259.3137402</v>
       </c>
       <c r="N72">
-        <v>-153.9947673333334</v>
+        <v>-157.6470735333334</v>
       </c>
       <c r="O72">
-        <v>-38.49869183333334</v>
+        <v>-39.41176838333334</v>
       </c>
       <c r="P72">
-        <v>-115.4960755</v>
+        <v>-118.23530515</v>
       </c>
       <c r="Q72">
-        <v>-106.4960755</v>
+        <v>-109.23530515</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3100631151169068</v>
+        <v>0.3191756363278347</v>
       </c>
       <c r="T72">
-        <v>2.555626294827062</v>
+        <v>2.643751339476272</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09941533327496968</v>
+        <v>0.09801511731335039</v>
       </c>
       <c r="W72">
-        <v>0.2123578644137622</v>
+        <v>0.212688035337512</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3976613330998787</v>
+        <v>0.3920604692534015</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2435694396247056</v>
+        <v>0.2454694396247055</v>
       </c>
       <c r="C73">
-        <v>-271.5735949803009</v>
+        <v>-292.3518684491023</v>
       </c>
       <c r="D73">
-        <v>555.845405019699</v>
+        <v>550.5561315508976</v>
       </c>
       <c r="E73">
-        <v>955.4189999999999</v>
+        <v>970.9079999999999</v>
       </c>
       <c r="F73">
-        <v>1099.719</v>
+        <v>1115.208</v>
       </c>
       <c r="G73">
         <v>272.3</v>
@@ -7273,37 +7273,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M73">
-        <v>259.3137402</v>
+        <v>262.9660464</v>
       </c>
       <c r="N73">
-        <v>-157.6470735333333</v>
+        <v>-161.2993797333333</v>
       </c>
       <c r="O73">
-        <v>-39.41176838333332</v>
+        <v>-40.32484493333332</v>
       </c>
       <c r="P73">
-        <v>-118.23530515</v>
+        <v>-120.9745348</v>
       </c>
       <c r="Q73">
-        <v>-109.23530515</v>
+        <v>-111.9745348</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3191756363278346</v>
+        <v>0.3289390519109715</v>
       </c>
       <c r="T73">
-        <v>2.643751339476271</v>
+        <v>2.738171030171852</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09801511731335041</v>
+        <v>0.09665379623955388</v>
       </c>
       <c r="W73">
-        <v>0.212688035337512</v>
+        <v>0.2130090348467132</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3920604692534017</v>
+        <v>0.3866151849582156</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2454694396247055</v>
+        <v>0.2473694396247055</v>
       </c>
       <c r="C74">
-        <v>-292.3518684491023</v>
+        <v>-313.0304281953333</v>
       </c>
       <c r="D74">
-        <v>550.5561315508976</v>
+        <v>545.3665718046666</v>
       </c>
       <c r="E74">
-        <v>970.9079999999999</v>
+        <v>986.3969999999999</v>
       </c>
       <c r="F74">
-        <v>1115.208</v>
+        <v>1130.697</v>
       </c>
       <c r="G74">
         <v>272.3</v>
@@ -7355,37 +7355,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M74">
-        <v>262.9660464</v>
+        <v>266.6183526</v>
       </c>
       <c r="N74">
-        <v>-161.2993797333333</v>
+        <v>-164.9516859333333</v>
       </c>
       <c r="O74">
-        <v>-40.32484493333332</v>
+        <v>-41.23792148333332</v>
       </c>
       <c r="P74">
-        <v>-120.9745348</v>
+        <v>-123.71376445</v>
       </c>
       <c r="Q74">
-        <v>-111.9745348</v>
+        <v>-114.71376445</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3289390519109715</v>
+        <v>0.3394256834632297</v>
       </c>
       <c r="T74">
-        <v>2.738171030171852</v>
+        <v>2.839584772030069</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09665379623955388</v>
+        <v>0.0953297716335326</v>
       </c>
       <c r="W74">
-        <v>0.2130090348467132</v>
+        <v>0.213321239848813</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3866151849582156</v>
+        <v>0.3813190865341304</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2473694396247055</v>
+        <v>0.2492694396247055</v>
       </c>
       <c r="C75">
-        <v>-313.0304281953333</v>
+        <v>-333.6120676027062</v>
       </c>
       <c r="D75">
-        <v>545.3665718046666</v>
+        <v>540.2739323972937</v>
       </c>
       <c r="E75">
-        <v>986.3969999999999</v>
+        <v>1001.886</v>
       </c>
       <c r="F75">
-        <v>1130.697</v>
+        <v>1146.186</v>
       </c>
       <c r="G75">
         <v>272.3</v>
@@ -7437,37 +7437,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M75">
-        <v>266.6183526</v>
+        <v>270.2706588</v>
       </c>
       <c r="N75">
-        <v>-164.9516859333333</v>
+        <v>-168.6039921333333</v>
       </c>
       <c r="O75">
-        <v>-41.23792148333332</v>
+        <v>-42.15099803333332</v>
       </c>
       <c r="P75">
-        <v>-123.71376445</v>
+        <v>-126.4529941</v>
       </c>
       <c r="Q75">
-        <v>-114.71376445</v>
+        <v>-117.4529941</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3394256834632297</v>
+        <v>0.3507189789810462</v>
       </c>
       <c r="T75">
-        <v>2.839584772030069</v>
+        <v>2.948799570954302</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0953297716335326</v>
+        <v>0.09404153147632269</v>
       </c>
       <c r="W75">
-        <v>0.213321239848813</v>
+        <v>0.2136250068778831</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3813190865341304</v>
+        <v>0.3761661259052909</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2492694396247055</v>
+        <v>0.2511694396247055</v>
       </c>
       <c r="C76">
-        <v>-333.6120676027062</v>
+        <v>-354.0994766816359</v>
       </c>
       <c r="D76">
-        <v>540.2739323972937</v>
+        <v>535.275523318364</v>
       </c>
       <c r="E76">
-        <v>1001.886</v>
+        <v>1017.375</v>
       </c>
       <c r="F76">
-        <v>1146.186</v>
+        <v>1161.675</v>
       </c>
       <c r="G76">
         <v>272.3</v>
@@ -7519,37 +7519,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M76">
-        <v>270.2706588</v>
+        <v>273.922965</v>
       </c>
       <c r="N76">
-        <v>-168.6039921333333</v>
+        <v>-172.2562983333333</v>
       </c>
       <c r="O76">
-        <v>-42.15099803333332</v>
+        <v>-43.06407458333332</v>
       </c>
       <c r="P76">
-        <v>-126.4529941</v>
+        <v>-129.19222375</v>
       </c>
       <c r="Q76">
-        <v>-117.4529941</v>
+        <v>-120.19222375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3507189789810462</v>
+        <v>0.3629157381402881</v>
       </c>
       <c r="T76">
-        <v>2.948799570954302</v>
+        <v>3.066751553792475</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09404153147632269</v>
+        <v>0.09278764438997172</v>
       </c>
       <c r="W76">
-        <v>0.2136250068778831</v>
+        <v>0.2139206734528447</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3761661259052909</v>
+        <v>0.3711505775598869</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2511694396247055</v>
+        <v>0.2530694396247055</v>
       </c>
       <c r="C77">
-        <v>-354.0994766816359</v>
+        <v>-374.4952468072579</v>
       </c>
       <c r="D77">
-        <v>535.275523318364</v>
+        <v>530.3687531927421</v>
       </c>
       <c r="E77">
-        <v>1017.375</v>
+        <v>1032.864</v>
       </c>
       <c r="F77">
-        <v>1161.675</v>
+        <v>1177.164</v>
       </c>
       <c r="G77">
         <v>272.3</v>
@@ -7601,37 +7601,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M77">
-        <v>273.922965</v>
+        <v>277.5752712</v>
       </c>
       <c r="N77">
-        <v>-172.2562983333333</v>
+        <v>-175.9086045333333</v>
       </c>
       <c r="O77">
-        <v>-43.06407458333332</v>
+        <v>-43.97715113333334</v>
       </c>
       <c r="P77">
-        <v>-129.19222375</v>
+        <v>-131.9314534</v>
       </c>
       <c r="Q77">
-        <v>-120.19222375</v>
+        <v>-122.9314534</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3629157381402881</v>
+        <v>0.3761288938961335</v>
       </c>
       <c r="T77">
-        <v>3.066751553792475</v>
+        <v>3.194532868533828</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09278764438997172</v>
+        <v>0.09156675433220891</v>
       </c>
       <c r="W77">
-        <v>0.2139206734528447</v>
+        <v>0.2142085593284651</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3711505775598869</v>
+        <v>0.3662670173288357</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2530694396247055</v>
+        <v>0.2549694396247055</v>
       </c>
       <c r="C78">
-        <v>-374.4952468072579</v>
+        <v>-394.8018751992174</v>
       </c>
       <c r="D78">
-        <v>530.3687531927421</v>
+        <v>525.5511248007826</v>
       </c>
       <c r="E78">
-        <v>1032.864</v>
+        <v>1048.353</v>
       </c>
       <c r="F78">
-        <v>1177.164</v>
+        <v>1192.653</v>
       </c>
       <c r="G78">
         <v>272.3</v>
@@ -7683,37 +7683,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M78">
-        <v>277.5752712</v>
+        <v>281.2275774</v>
       </c>
       <c r="N78">
-        <v>-175.9086045333333</v>
+        <v>-179.5609107333333</v>
       </c>
       <c r="O78">
-        <v>-43.97715113333334</v>
+        <v>-44.89022768333334</v>
       </c>
       <c r="P78">
-        <v>-131.9314534</v>
+        <v>-134.67068305</v>
       </c>
       <c r="Q78">
-        <v>-122.9314534</v>
+        <v>-125.67068305</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3761288938961335</v>
+        <v>0.3904910197177044</v>
       </c>
       <c r="T78">
-        <v>3.194532868533828</v>
+        <v>3.333425601948341</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09156675433220891</v>
+        <v>0.09037757570451789</v>
       </c>
       <c r="W78">
-        <v>0.2142085593284651</v>
+        <v>0.2144889676488747</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3662670173288357</v>
+        <v>0.3615103028180716</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2549694396247055</v>
+        <v>0.2568694396247055</v>
       </c>
       <c r="C79">
-        <v>-394.8018751992174</v>
+        <v>-415.0217691595033</v>
       </c>
       <c r="D79">
-        <v>525.5511248007826</v>
+        <v>520.8202308404965</v>
       </c>
       <c r="E79">
-        <v>1048.353</v>
+        <v>1063.842</v>
       </c>
       <c r="F79">
-        <v>1192.653</v>
+        <v>1208.142</v>
       </c>
       <c r="G79">
         <v>272.3</v>
@@ -7765,37 +7765,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M79">
-        <v>281.2275774</v>
+        <v>284.8798836</v>
       </c>
       <c r="N79">
-        <v>-179.5609107333333</v>
+        <v>-183.2132169333333</v>
       </c>
       <c r="O79">
-        <v>-44.89022768333334</v>
+        <v>-45.80330423333332</v>
       </c>
       <c r="P79">
-        <v>-134.67068305</v>
+        <v>-137.4099126999999</v>
       </c>
       <c r="Q79">
-        <v>-125.67068305</v>
+        <v>-128.4099126999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3904910197177044</v>
+        <v>0.4061587933412364</v>
       </c>
       <c r="T79">
-        <v>3.333425601948341</v>
+        <v>3.484944947491448</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09037757570451789</v>
+        <v>0.08921888883651127</v>
       </c>
       <c r="W79">
-        <v>0.2144889676488747</v>
+        <v>0.2147621860123506</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3615103028180716</v>
+        <v>0.3568755553460451</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2568694396247055</v>
+        <v>0.2587694396247056</v>
       </c>
       <c r="C80">
-        <v>-415.0217691595033</v>
+        <v>-435.1572500834366</v>
       </c>
       <c r="D80">
-        <v>520.8202308404965</v>
+        <v>516.1737499165633</v>
       </c>
       <c r="E80">
-        <v>1063.842</v>
+        <v>1079.331</v>
       </c>
       <c r="F80">
-        <v>1208.142</v>
+        <v>1223.631</v>
       </c>
       <c r="G80">
         <v>272.3</v>
@@ -7847,37 +7847,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M80">
-        <v>284.8798836</v>
+        <v>288.5321898</v>
       </c>
       <c r="N80">
-        <v>-183.2132169333333</v>
+        <v>-186.8655231333333</v>
       </c>
       <c r="O80">
-        <v>-45.80330423333332</v>
+        <v>-46.71638078333332</v>
       </c>
       <c r="P80">
-        <v>-137.4099126999999</v>
+        <v>-140.14914235</v>
       </c>
       <c r="Q80">
-        <v>-128.4099126999999</v>
+        <v>-131.14914235</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4061587933412364</v>
+        <v>0.4233187358812954</v>
       </c>
       <c r="T80">
-        <v>3.484944947491448</v>
+        <v>3.650894706895804</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08921888883651127</v>
+        <v>0.0880895358132643</v>
       </c>
       <c r="W80">
-        <v>0.2147621860123506</v>
+        <v>0.2150284874552323</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3568755553460451</v>
+        <v>0.3523581432530573</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2587694396247056</v>
+        <v>0.2606694396247055</v>
       </c>
       <c r="C81">
-        <v>-435.1572500834366</v>
+        <v>-455.210557257851</v>
       </c>
       <c r="D81">
-        <v>516.1737499165633</v>
+        <v>511.6094427421489</v>
       </c>
       <c r="E81">
-        <v>1079.331</v>
+        <v>1094.82</v>
       </c>
       <c r="F81">
-        <v>1223.631</v>
+        <v>1239.12</v>
       </c>
       <c r="G81">
         <v>272.3</v>
@@ -7929,37 +7929,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M81">
-        <v>288.5321898</v>
+        <v>292.184496</v>
       </c>
       <c r="N81">
-        <v>-186.8655231333333</v>
+        <v>-190.5178293333333</v>
       </c>
       <c r="O81">
-        <v>-46.71638078333332</v>
+        <v>-47.62945733333332</v>
       </c>
       <c r="P81">
-        <v>-140.14914235</v>
+        <v>-142.8883719999999</v>
       </c>
       <c r="Q81">
-        <v>-131.14914235</v>
+        <v>-133.8883719999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4233187358812954</v>
+        <v>0.4421946726753602</v>
       </c>
       <c r="T81">
-        <v>3.650894706895804</v>
+        <v>3.833439442240594</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0880895358132643</v>
+        <v>0.08698841661559849</v>
       </c>
       <c r="W81">
-        <v>0.2150284874552323</v>
+        <v>0.2152881313620419</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3523581432530573</v>
+        <v>0.347953666462394</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2606694396247055</v>
+        <v>0.2625694396247056</v>
       </c>
       <c r="C82">
-        <v>-455.210557257851</v>
+        <v>-475.1838514595293</v>
       </c>
       <c r="D82">
-        <v>511.6094427421489</v>
+        <v>507.1251485404706</v>
       </c>
       <c r="E82">
-        <v>1094.82</v>
+        <v>1110.309</v>
       </c>
       <c r="F82">
-        <v>1239.12</v>
+        <v>1254.609</v>
       </c>
       <c r="G82">
         <v>272.3</v>
@@ -8011,37 +8011,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M82">
-        <v>292.184496</v>
+        <v>295.8368022</v>
       </c>
       <c r="N82">
-        <v>-190.5178293333333</v>
+        <v>-194.1701355333333</v>
       </c>
       <c r="O82">
-        <v>-47.62945733333332</v>
+        <v>-48.54253388333333</v>
       </c>
       <c r="P82">
-        <v>-142.8883719999999</v>
+        <v>-145.62760165</v>
       </c>
       <c r="Q82">
-        <v>-133.8883719999999</v>
+        <v>-136.62760165</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4421946726753602</v>
+        <v>0.4630575501845897</v>
       </c>
       <c r="T82">
-        <v>3.833439442240594</v>
+        <v>4.035199412884836</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08698841661559849</v>
+        <v>0.0859144855462701</v>
       </c>
       <c r="W82">
-        <v>0.2152881313620419</v>
+        <v>0.2155413643081895</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.347953666462394</v>
+        <v>0.3436579421850804</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2625694396247056</v>
+        <v>0.2644694396247055</v>
       </c>
       <c r="C83">
-        <v>-475.1838514595293</v>
+        <v>-495.0792183660369</v>
       </c>
       <c r="D83">
-        <v>507.1251485404706</v>
+        <v>502.718781633963</v>
       </c>
       <c r="E83">
-        <v>1110.309</v>
+        <v>1125.798</v>
       </c>
       <c r="F83">
-        <v>1254.609</v>
+        <v>1270.098</v>
       </c>
       <c r="G83">
         <v>272.3</v>
@@ -8093,37 +8093,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M83">
-        <v>295.8368022</v>
+        <v>299.4891084</v>
       </c>
       <c r="N83">
-        <v>-194.1701355333333</v>
+        <v>-197.8224417333333</v>
       </c>
       <c r="O83">
-        <v>-48.54253388333333</v>
+        <v>-49.45561043333333</v>
       </c>
       <c r="P83">
-        <v>-145.62760165</v>
+        <v>-148.3668313</v>
       </c>
       <c r="Q83">
-        <v>-136.62760165</v>
+        <v>-139.3668313</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4630575501845897</v>
+        <v>0.4862385251948447</v>
       </c>
       <c r="T83">
-        <v>4.035199412884836</v>
+        <v>4.259377158045105</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0859144855462701</v>
+        <v>0.08486674791765705</v>
       </c>
       <c r="W83">
-        <v>0.2155413643081895</v>
+        <v>0.2157884208410165</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3436579421850804</v>
+        <v>0.3394669916706282</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2644694396247055</v>
+        <v>0.2663694396247056</v>
       </c>
       <c r="C84">
-        <v>-495.0792183660369</v>
+        <v>-514.8986717902726</v>
       </c>
       <c r="D84">
-        <v>502.718781633963</v>
+        <v>498.3883282097273</v>
       </c>
       <c r="E84">
-        <v>1125.798</v>
+        <v>1141.287</v>
       </c>
       <c r="F84">
-        <v>1270.098</v>
+        <v>1285.587</v>
       </c>
       <c r="G84">
         <v>272.3</v>
@@ -8175,37 +8175,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M84">
-        <v>299.4891084</v>
+        <v>303.1414146</v>
       </c>
       <c r="N84">
-        <v>-197.8224417333333</v>
+        <v>-201.4747479333333</v>
       </c>
       <c r="O84">
-        <v>-49.45561043333333</v>
+        <v>-50.36868698333333</v>
       </c>
       <c r="P84">
-        <v>-148.3668313</v>
+        <v>-151.10606095</v>
       </c>
       <c r="Q84">
-        <v>-139.3668313</v>
+        <v>-142.10606095</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4862385251948447</v>
+        <v>0.512146673735718</v>
       </c>
       <c r="T84">
-        <v>4.259377158045105</v>
+        <v>4.50992875557717</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08486674791765705</v>
+        <v>0.0838442569788901</v>
       </c>
       <c r="W84">
-        <v>0.2157884208410165</v>
+        <v>0.2160295242043777</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3394669916706282</v>
+        <v>0.3353770279155605</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2663694396247056</v>
+        <v>0.2682694396247055</v>
       </c>
       <c r="C85">
-        <v>-514.8986717902726</v>
+        <v>-534.644156749267</v>
       </c>
       <c r="D85">
-        <v>498.3883282097273</v>
+        <v>494.131843250733</v>
       </c>
       <c r="E85">
-        <v>1141.287</v>
+        <v>1156.776</v>
       </c>
       <c r="F85">
-        <v>1285.587</v>
+        <v>1301.076</v>
       </c>
       <c r="G85">
         <v>272.3</v>
@@ -8257,37 +8257,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M85">
-        <v>303.1414146</v>
+        <v>306.7937208</v>
       </c>
       <c r="N85">
-        <v>-201.4747479333333</v>
+        <v>-205.1270541333333</v>
       </c>
       <c r="O85">
-        <v>-50.36868698333333</v>
+        <v>-51.28176353333333</v>
       </c>
       <c r="P85">
-        <v>-151.10606095</v>
+        <v>-153.8452906</v>
       </c>
       <c r="Q85">
-        <v>-142.10606095</v>
+        <v>-144.8452906</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.512146673735718</v>
+        <v>0.5412933408442003</v>
       </c>
       <c r="T85">
-        <v>4.50992875557717</v>
+        <v>4.791799302800744</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0838442569788901</v>
+        <v>0.08284611106247473</v>
       </c>
       <c r="W85">
-        <v>0.2160295242043777</v>
+        <v>0.2162648870114685</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3353770279155605</v>
+        <v>0.331384444249899</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2682694396247055</v>
+        <v>0.2701694396247056</v>
       </c>
       <c r="C86">
-        <v>-534.6441567492668</v>
+        <v>-554.3175523770617</v>
       </c>
       <c r="D86">
-        <v>494.131843250733</v>
+        <v>489.9474476229381</v>
       </c>
       <c r="E86">
-        <v>1156.776</v>
+        <v>1172.265</v>
       </c>
       <c r="F86">
-        <v>1301.076</v>
+        <v>1316.565</v>
       </c>
       <c r="G86">
         <v>272.3</v>
@@ -8339,37 +8339,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M86">
-        <v>306.7937208</v>
+        <v>310.446027</v>
       </c>
       <c r="N86">
-        <v>-205.1270541333333</v>
+        <v>-208.7793603333333</v>
       </c>
       <c r="O86">
-        <v>-51.28176353333332</v>
+        <v>-52.19484008333332</v>
       </c>
       <c r="P86">
-        <v>-153.8452905999999</v>
+        <v>-156.58452025</v>
       </c>
       <c r="Q86">
-        <v>-144.8452905999999</v>
+        <v>-147.58452025</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5412933408442001</v>
+        <v>0.5743262302338135</v>
       </c>
       <c r="T86">
-        <v>4.791799302800741</v>
+        <v>5.111252589654124</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08284611106247475</v>
+        <v>0.08187145093232799</v>
       </c>
       <c r="W86">
-        <v>0.2162648870114685</v>
+        <v>0.2164947118701571</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3313844442498991</v>
+        <v>0.327485803729312</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2701694396247056</v>
+        <v>0.2720694396247055</v>
       </c>
       <c r="C87">
-        <v>-554.3175523770617</v>
+        <v>-573.9206746908288</v>
       </c>
       <c r="D87">
-        <v>489.9474476229381</v>
+        <v>485.833325309171</v>
       </c>
       <c r="E87">
-        <v>1172.265</v>
+        <v>1187.754</v>
       </c>
       <c r="F87">
-        <v>1316.565</v>
+        <v>1332.054</v>
       </c>
       <c r="G87">
         <v>272.3</v>
@@ -8421,37 +8421,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M87">
-        <v>310.446027</v>
+        <v>314.0983332</v>
       </c>
       <c r="N87">
-        <v>-208.7793603333333</v>
+        <v>-212.4316665333333</v>
       </c>
       <c r="O87">
-        <v>-52.19484008333332</v>
+        <v>-53.10791663333332</v>
       </c>
       <c r="P87">
-        <v>-156.58452025</v>
+        <v>-159.3237498999999</v>
       </c>
       <c r="Q87">
-        <v>-147.58452025</v>
+        <v>-150.3237498999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5743262302338135</v>
+        <v>0.6120781038219429</v>
       </c>
       <c r="T87">
-        <v>5.111252589654124</v>
+        <v>5.476342060343704</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08187145093232799</v>
+        <v>0.08091945731683581</v>
       </c>
       <c r="W87">
-        <v>0.2164947118701571</v>
+        <v>0.2167191919646901</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.327485803729312</v>
+        <v>0.3236778292673432</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2720694396247055</v>
+        <v>0.2739694396247055</v>
       </c>
       <c r="C88">
-        <v>-573.9206746908288</v>
+        <v>-593.4552792187872</v>
       </c>
       <c r="D88">
-        <v>485.833325309171</v>
+        <v>481.7877207812127</v>
       </c>
       <c r="E88">
-        <v>1187.754</v>
+        <v>1203.243</v>
       </c>
       <c r="F88">
-        <v>1332.054</v>
+        <v>1347.543</v>
       </c>
       <c r="G88">
         <v>272.3</v>
@@ -8503,37 +8503,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M88">
-        <v>314.0983332</v>
+        <v>317.7506394</v>
       </c>
       <c r="N88">
-        <v>-212.4316665333333</v>
+        <v>-216.0839727333333</v>
       </c>
       <c r="O88">
-        <v>-53.10791663333332</v>
+        <v>-54.02099318333333</v>
       </c>
       <c r="P88">
-        <v>-159.3237498999999</v>
+        <v>-162.06297955</v>
       </c>
       <c r="Q88">
-        <v>-150.3237498999999</v>
+        <v>-153.06297955</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6120781038219429</v>
+        <v>0.6556379579620925</v>
       </c>
       <c r="T88">
-        <v>5.476342060343704</v>
+        <v>5.897599141908604</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08091945731683581</v>
+        <v>0.07998934861204458</v>
       </c>
       <c r="W88">
-        <v>0.2167191919646901</v>
+        <v>0.2169385115972799</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3236778292673432</v>
+        <v>0.3199573944481784</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2739694396247055</v>
+        <v>0.2758694396247056</v>
       </c>
       <c r="C89">
-        <v>-593.4552792187872</v>
+        <v>-612.9230634979054</v>
       </c>
       <c r="D89">
-        <v>481.7877207812127</v>
+        <v>477.8089365020945</v>
       </c>
       <c r="E89">
-        <v>1203.243</v>
+        <v>1218.732</v>
       </c>
       <c r="F89">
-        <v>1347.543</v>
+        <v>1363.032</v>
       </c>
       <c r="G89">
         <v>272.3</v>
@@ -8585,37 +8585,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M89">
-        <v>317.7506394</v>
+        <v>321.4029456</v>
       </c>
       <c r="N89">
-        <v>-216.0839727333333</v>
+        <v>-219.7362789333333</v>
       </c>
       <c r="O89">
-        <v>-54.02099318333333</v>
+        <v>-54.93406973333333</v>
       </c>
       <c r="P89">
-        <v>-162.06297955</v>
+        <v>-164.8022092</v>
       </c>
       <c r="Q89">
-        <v>-153.06297955</v>
+        <v>-155.8022092</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6556379579620925</v>
+        <v>0.7064577877922669</v>
       </c>
       <c r="T89">
-        <v>5.897599141908604</v>
+        <v>6.389065737067655</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07998934861204458</v>
+        <v>0.07908037874145316</v>
       </c>
       <c r="W89">
-        <v>0.2169385115972799</v>
+        <v>0.2171528466927654</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3199573944481784</v>
+        <v>0.3163215149658127</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2758694396247056</v>
+        <v>0.2777694396247055</v>
       </c>
       <c r="C90">
-        <v>-612.9230634979054</v>
+        <v>-632.3256694488562</v>
       </c>
       <c r="D90">
-        <v>477.8089365020945</v>
+        <v>473.8953305511438</v>
       </c>
       <c r="E90">
-        <v>1218.732</v>
+        <v>1234.221</v>
       </c>
       <c r="F90">
-        <v>1363.032</v>
+        <v>1378.521</v>
       </c>
       <c r="G90">
         <v>272.3</v>
@@ -8667,37 +8667,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M90">
-        <v>321.4029456</v>
+        <v>325.0552518</v>
       </c>
       <c r="N90">
-        <v>-219.7362789333333</v>
+        <v>-223.3885851333333</v>
       </c>
       <c r="O90">
-        <v>-54.93406973333333</v>
+        <v>-55.84714628333333</v>
       </c>
       <c r="P90">
-        <v>-164.8022092</v>
+        <v>-167.54143885</v>
       </c>
       <c r="Q90">
-        <v>-155.8022092</v>
+        <v>-158.54143885</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7064577877922669</v>
+        <v>0.7665175866824728</v>
       </c>
       <c r="T90">
-        <v>6.389065737067655</v>
+        <v>6.969889894982896</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07908037874145316</v>
+        <v>0.07819183516008853</v>
       </c>
       <c r="W90">
-        <v>0.2171528466927654</v>
+        <v>0.2173623652692511</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3163215149658127</v>
+        <v>0.3127673406403542</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2777694396247055</v>
+        <v>0.2796694396247055</v>
       </c>
       <c r="C91">
-        <v>-632.3256694488562</v>
+        <v>-651.6646856352039</v>
       </c>
       <c r="D91">
-        <v>473.8953305511438</v>
+        <v>470.0453143647961</v>
       </c>
       <c r="E91">
-        <v>1234.221</v>
+        <v>1249.71</v>
       </c>
       <c r="F91">
-        <v>1378.521</v>
+        <v>1394.01</v>
       </c>
       <c r="G91">
         <v>272.3</v>
@@ -8749,37 +8749,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M91">
-        <v>325.0552518</v>
+        <v>328.707558</v>
       </c>
       <c r="N91">
-        <v>-223.3885851333333</v>
+        <v>-227.0408913333333</v>
       </c>
       <c r="O91">
-        <v>-55.84714628333333</v>
+        <v>-56.76022283333333</v>
       </c>
       <c r="P91">
-        <v>-167.54143885</v>
+        <v>-170.2806685</v>
       </c>
       <c r="Q91">
-        <v>-158.54143885</v>
+        <v>-161.2806685</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7665175866824728</v>
+        <v>0.8385893453507204</v>
       </c>
       <c r="T91">
-        <v>6.969889894982896</v>
+        <v>7.666878884481187</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07819183516008853</v>
+        <v>0.0773230369916431</v>
       </c>
       <c r="W91">
-        <v>0.2173623652692511</v>
+        <v>0.2175672278773706</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3127673406403542</v>
+        <v>0.3092921479665725</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2796694396247055</v>
+        <v>0.2815694396247055</v>
       </c>
       <c r="C92">
-        <v>-651.6646856352039</v>
+        <v>-670.9416494133541</v>
       </c>
       <c r="D92">
-        <v>470.0453143647961</v>
+        <v>466.2573505866459</v>
       </c>
       <c r="E92">
-        <v>1249.71</v>
+        <v>1265.199</v>
       </c>
       <c r="F92">
-        <v>1394.01</v>
+        <v>1409.499</v>
       </c>
       <c r="G92">
         <v>272.3</v>
@@ -8831,37 +8831,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M92">
-        <v>328.707558</v>
+        <v>332.3598642</v>
       </c>
       <c r="N92">
-        <v>-227.0408913333333</v>
+        <v>-230.6931975333333</v>
       </c>
       <c r="O92">
-        <v>-56.76022283333333</v>
+        <v>-57.67329938333333</v>
       </c>
       <c r="P92">
-        <v>-170.2806685</v>
+        <v>-173.01989815</v>
       </c>
       <c r="Q92">
-        <v>-161.2806685</v>
+        <v>-164.01989815</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8385893453507204</v>
+        <v>0.9266770503896894</v>
       </c>
       <c r="T92">
-        <v>7.666878884481187</v>
+        <v>8.518754316090209</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0773230369916431</v>
+        <v>0.07647333328843822</v>
       </c>
       <c r="W92">
-        <v>0.2175672278773706</v>
+        <v>0.2177675880105863</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3092921479665725</v>
+        <v>0.3058933331537529</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2815694396247055</v>
+        <v>0.2834694396247056</v>
       </c>
       <c r="C93">
-        <v>-670.9416494133541</v>
+        <v>-690.1580489793791</v>
       </c>
       <c r="D93">
-        <v>466.2573505866459</v>
+        <v>462.5299510206206</v>
       </c>
       <c r="E93">
-        <v>1265.199</v>
+        <v>1280.688</v>
       </c>
       <c r="F93">
-        <v>1409.499</v>
+        <v>1424.988</v>
       </c>
       <c r="G93">
         <v>272.3</v>
@@ -8913,37 +8913,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M93">
-        <v>332.3598642</v>
+        <v>336.0121703999999</v>
       </c>
       <c r="N93">
-        <v>-230.6931975333333</v>
+        <v>-234.3455037333333</v>
       </c>
       <c r="O93">
-        <v>-57.67329938333333</v>
+        <v>-58.58637593333331</v>
       </c>
       <c r="P93">
-        <v>-173.01989815</v>
+        <v>-175.7591277999999</v>
       </c>
       <c r="Q93">
-        <v>-164.01989815</v>
+        <v>-166.7591277999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9266770503896894</v>
+        <v>1.036786681688401</v>
       </c>
       <c r="T93">
-        <v>8.518754316090209</v>
+        <v>9.583598605601487</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07647333328843822</v>
+        <v>0.07564210140486825</v>
       </c>
       <c r="W93">
-        <v>0.2177675880105863</v>
+        <v>0.2179635924887321</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3058933331537529</v>
+        <v>0.3025684056194731</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2834694396247056</v>
+        <v>0.2853694396247055</v>
       </c>
       <c r="C94">
-        <v>-690.1580489793791</v>
+        <v>-709.3153253184475</v>
       </c>
       <c r="D94">
-        <v>462.5299510206206</v>
+        <v>458.8616746815522</v>
       </c>
       <c r="E94">
-        <v>1280.688</v>
+        <v>1296.177</v>
       </c>
       <c r="F94">
-        <v>1424.988</v>
+        <v>1440.477</v>
       </c>
       <c r="G94">
         <v>272.3</v>
@@ -8995,37 +8995,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M94">
-        <v>336.0121703999999</v>
+        <v>339.6644766</v>
       </c>
       <c r="N94">
-        <v>-234.3455037333333</v>
+        <v>-237.9978099333333</v>
       </c>
       <c r="O94">
-        <v>-58.58637593333331</v>
+        <v>-59.49945248333333</v>
       </c>
       <c r="P94">
-        <v>-175.7591277999999</v>
+        <v>-178.49835745</v>
       </c>
       <c r="Q94">
-        <v>-166.7591277999999</v>
+        <v>-169.49835745</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.036786681688401</v>
+        <v>1.178356207643887</v>
       </c>
       <c r="T94">
-        <v>9.583598605601487</v>
+        <v>10.95268412068742</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07564210140486825</v>
+        <v>0.07482874547578364</v>
       </c>
       <c r="W94">
-        <v>0.2179635924887321</v>
+        <v>0.2181553818168102</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3025684056194731</v>
+        <v>0.2993149819031345</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2853694396247055</v>
+        <v>0.2872694396247055</v>
       </c>
       <c r="C95">
-        <v>-709.3153253184475</v>
+        <v>-728.414874062214</v>
       </c>
       <c r="D95">
-        <v>458.8616746815522</v>
+        <v>455.2511259377858</v>
       </c>
       <c r="E95">
-        <v>1296.177</v>
+        <v>1311.666</v>
       </c>
       <c r="F95">
-        <v>1440.477</v>
+        <v>1455.966</v>
       </c>
       <c r="G95">
         <v>272.3</v>
@@ -9077,37 +9077,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M95">
-        <v>339.6644766</v>
+        <v>343.3167828</v>
       </c>
       <c r="N95">
-        <v>-237.9978099333333</v>
+        <v>-241.6501161333333</v>
       </c>
       <c r="O95">
-        <v>-59.49945248333333</v>
+        <v>-60.41252903333333</v>
       </c>
       <c r="P95">
-        <v>-178.49835745</v>
+        <v>-181.2375871</v>
       </c>
       <c r="Q95">
-        <v>-169.49835745</v>
+        <v>-172.2375871</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.178356207643887</v>
+        <v>1.367115575584535</v>
       </c>
       <c r="T95">
-        <v>10.95268412068742</v>
+        <v>12.77813147413532</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07482874547578364</v>
+        <v>0.0740326949919987</v>
       </c>
       <c r="W95">
-        <v>0.2181553818168102</v>
+        <v>0.2183430905208867</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2993149819031345</v>
+        <v>0.2961307799679949</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2872694396247055</v>
+        <v>0.2891694396247056</v>
       </c>
       <c r="C96">
-        <v>-728.414874062214</v>
+        <v>-747.458047259209</v>
       </c>
       <c r="D96">
-        <v>455.2511259377858</v>
+        <v>451.6969527407909</v>
       </c>
       <c r="E96">
-        <v>1311.666</v>
+        <v>1327.155</v>
       </c>
       <c r="F96">
-        <v>1455.966</v>
+        <v>1471.455</v>
       </c>
       <c r="G96">
         <v>272.3</v>
@@ -9159,37 +9159,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M96">
-        <v>343.3167828</v>
+        <v>346.969089</v>
       </c>
       <c r="N96">
-        <v>-241.6501161333333</v>
+        <v>-245.3024223333333</v>
       </c>
       <c r="O96">
-        <v>-60.41252903333333</v>
+        <v>-61.32560558333333</v>
       </c>
       <c r="P96">
-        <v>-181.2375871</v>
+        <v>-183.97681675</v>
       </c>
       <c r="Q96">
-        <v>-172.2375871</v>
+        <v>-174.97681675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.367115575584535</v>
+        <v>1.631378690701443</v>
       </c>
       <c r="T96">
-        <v>12.77813147413532</v>
+        <v>15.33375776896239</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0740326949919987</v>
+        <v>0.07325340346576714</v>
       </c>
       <c r="W96">
-        <v>0.2183430905208867</v>
+        <v>0.2185268474627721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2961307799679949</v>
+        <v>0.2930136138630686</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2891694396247056</v>
+        <v>0.2910694396247056</v>
       </c>
       <c r="C97">
-        <v>-747.458047259209</v>
+        <v>-766.4461550629399</v>
       </c>
       <c r="D97">
-        <v>451.6969527407909</v>
+        <v>448.19784493706</v>
       </c>
       <c r="E97">
-        <v>1327.155</v>
+        <v>1342.644</v>
       </c>
       <c r="F97">
-        <v>1471.455</v>
+        <v>1486.944</v>
       </c>
       <c r="G97">
         <v>272.3</v>
@@ -9241,37 +9241,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M97">
-        <v>346.969089</v>
+        <v>350.6213952</v>
       </c>
       <c r="N97">
-        <v>-245.3024223333333</v>
+        <v>-248.9547285333333</v>
       </c>
       <c r="O97">
-        <v>-61.32560558333333</v>
+        <v>-62.23868213333333</v>
       </c>
       <c r="P97">
-        <v>-183.97681675</v>
+        <v>-186.7160464</v>
       </c>
       <c r="Q97">
-        <v>-174.97681675</v>
+        <v>-177.7160464</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.631378690701443</v>
+        <v>2.027773363376804</v>
       </c>
       <c r="T97">
-        <v>15.33375776896239</v>
+        <v>19.167197211203</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07325340346576714</v>
+        <v>0.0724903471796654</v>
       </c>
       <c r="W97">
-        <v>0.2185268474627721</v>
+        <v>0.2187067761350349</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2930136138630686</v>
+        <v>0.2899613887186616</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2910694396247056</v>
+        <v>0.2929694396247056</v>
       </c>
       <c r="C98">
-        <v>-766.4461550629396</v>
+        <v>-785.3804673421334</v>
       </c>
       <c r="D98">
-        <v>448.19784493706</v>
+        <v>444.7525326578663</v>
       </c>
       <c r="E98">
-        <v>1342.644</v>
+        <v>1358.133</v>
       </c>
       <c r="F98">
-        <v>1486.944</v>
+        <v>1502.433</v>
       </c>
       <c r="G98">
         <v>272.3</v>
@@ -9323,37 +9323,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M98">
-        <v>350.6213951999999</v>
+        <v>354.2737013999999</v>
       </c>
       <c r="N98">
-        <v>-248.9547285333333</v>
+        <v>-252.6070347333333</v>
       </c>
       <c r="O98">
-        <v>-62.23868213333331</v>
+        <v>-63.15175868333331</v>
       </c>
       <c r="P98">
-        <v>-186.7160463999999</v>
+        <v>-189.45527605</v>
       </c>
       <c r="Q98">
-        <v>-177.7160463999999</v>
+        <v>-180.45527605</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.027773363376799</v>
+        <v>2.688431151169065</v>
       </c>
       <c r="T98">
-        <v>19.16719721120295</v>
+        <v>25.5562629482706</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07249034717966542</v>
+        <v>0.07174302401286474</v>
       </c>
       <c r="W98">
-        <v>0.2187067761350349</v>
+        <v>0.2188829949377665</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2899613887186617</v>
+        <v>0.286972096051459</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2929694396247056</v>
+        <v>0.2948694396247056</v>
       </c>
       <c r="C99">
-        <v>-785.3804673421334</v>
+        <v>-804.2622152172771</v>
       </c>
       <c r="D99">
-        <v>444.7525326578663</v>
+        <v>441.3597847827227</v>
       </c>
       <c r="E99">
-        <v>1358.133</v>
+        <v>1373.622</v>
       </c>
       <c r="F99">
-        <v>1502.433</v>
+        <v>1517.922</v>
       </c>
       <c r="G99">
         <v>272.3</v>
@@ -9405,37 +9405,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M99">
-        <v>354.2737013999999</v>
+        <v>357.9260076</v>
       </c>
       <c r="N99">
-        <v>-252.6070347333333</v>
+        <v>-256.2593409333333</v>
       </c>
       <c r="O99">
-        <v>-63.15175868333331</v>
+        <v>-64.06483523333333</v>
       </c>
       <c r="P99">
-        <v>-189.45527605</v>
+        <v>-192.1945057</v>
       </c>
       <c r="Q99">
-        <v>-180.45527605</v>
+        <v>-183.1945057</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.688431151169065</v>
+        <v>4.009746726753598</v>
       </c>
       <c r="T99">
-        <v>25.5562629482706</v>
+        <v>38.3343944224059</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07174302401286474</v>
+        <v>0.07101095233926406</v>
       </c>
       <c r="W99">
-        <v>0.2188829949377665</v>
+        <v>0.2190556174384015</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.286972096051459</v>
+        <v>0.2840438093570563</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2948694396247056</v>
+        <v>0.2967694396247055</v>
       </c>
       <c r="C100">
-        <v>-804.2622152172771</v>
+        <v>-823.0925925273638</v>
       </c>
       <c r="D100">
-        <v>441.3597847827227</v>
+        <v>438.0184074726361</v>
       </c>
       <c r="E100">
-        <v>1373.622</v>
+        <v>1389.111</v>
       </c>
       <c r="F100">
-        <v>1517.922</v>
+        <v>1533.411</v>
       </c>
       <c r="G100">
         <v>272.3</v>
@@ -9487,37 +9487,37 @@
         <v>101.6666666666667</v>
       </c>
       <c r="M100">
-        <v>357.9260076</v>
+        <v>361.5783138</v>
       </c>
       <c r="N100">
-        <v>-256.2593409333333</v>
+        <v>-259.9116471333333</v>
       </c>
       <c r="O100">
-        <v>-64.06483523333333</v>
+        <v>-64.97791178333333</v>
       </c>
       <c r="P100">
-        <v>-192.1945057</v>
+        <v>-194.93373535</v>
       </c>
       <c r="Q100">
-        <v>-183.1945057</v>
+        <v>-185.93373535</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.009746726753598</v>
+        <v>7.973693453507196</v>
       </c>
       <c r="T100">
-        <v>38.3343944224059</v>
+        <v>76.6687888448118</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07101095233926406</v>
+        <v>0.07029366999240282</v>
       </c>
       <c r="W100">
-        <v>0.2190556174384015</v>
+        <v>0.2192247526157914</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2840438093570563</v>
+        <v>0.2811746799696113</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2967694396247055</v>
-      </c>
-      <c r="C101">
-        <v>-823.0925925273638</v>
-      </c>
-      <c r="D101">
-        <v>438.0184074726361</v>
-      </c>
-      <c r="E101">
-        <v>1389.111</v>
-      </c>
-      <c r="F101">
-        <v>1533.411</v>
-      </c>
-      <c r="G101">
-        <v>272.3</v>
-      </c>
-      <c r="H101">
-        <v>1404.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>110.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>9</v>
-      </c>
-      <c r="L101">
-        <v>101.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>361.5783138</v>
-      </c>
-      <c r="N101">
-        <v>-259.9116471333333</v>
-      </c>
-      <c r="O101">
-        <v>-64.97791178333333</v>
-      </c>
-      <c r="P101">
-        <v>-194.93373535</v>
-      </c>
-      <c r="Q101">
-        <v>-185.93373535</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.973693453507196</v>
-      </c>
-      <c r="T101">
-        <v>76.6687888448118</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07029366999240282</v>
-      </c>
-      <c r="W101">
-        <v>0.2192247526157914</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2811746799696113</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
